--- a/outputs/VIC_negative_prices.xlsx
+++ b/outputs/VIC_negative_prices.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J85"/>
+  <dimension ref="A1:J86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3372,6 +3372,40 @@
         <v>0.35</v>
       </c>
     </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>May 2026</t>
+        </is>
+      </c>
+      <c r="B86" s="3" t="n">
+        <v>21.64</v>
+      </c>
+      <c r="C86" s="3" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="D86" s="3" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="E86" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F86" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G86" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H86" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I86" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J86" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3383,7 +3417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J85"/>
+  <dimension ref="A1:J86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -6306,8 +6340,42 @@
         <v>0.35</v>
       </c>
     </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>May 2026</t>
+        </is>
+      </c>
+      <c r="B86" s="3" t="n">
+        <v>21.64</v>
+      </c>
+      <c r="C86" s="3" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="D86" s="3" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="E86" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F86" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G86" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H86" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I86" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J86" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="B2:B85">
+  <conditionalFormatting sqref="B2:B86">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -6319,7 +6387,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C85">
+  <conditionalFormatting sqref="C2:C86">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
@@ -6331,7 +6399,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D85">
+  <conditionalFormatting sqref="D2:D86">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
@@ -6343,7 +6411,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E85">
+  <conditionalFormatting sqref="E2:E86">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="min"/>
@@ -6355,7 +6423,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F85">
+  <conditionalFormatting sqref="F2:F86">
     <cfRule type="colorScale" priority="5">
       <colorScale>
         <cfvo type="min"/>
@@ -6367,7 +6435,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G85">
+  <conditionalFormatting sqref="G2:G86">
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="min"/>
@@ -6379,7 +6447,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H85">
+  <conditionalFormatting sqref="H2:H86">
     <cfRule type="colorScale" priority="7">
       <colorScale>
         <cfvo type="min"/>
@@ -6391,7 +6459,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I85">
+  <conditionalFormatting sqref="I2:I86">
     <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="min"/>
@@ -6403,7 +6471,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J85">
+  <conditionalFormatting sqref="J2:J86">
     <cfRule type="colorScale" priority="9">
       <colorScale>
         <cfvo type="min"/>
@@ -6425,7 +6493,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K85"/>
+  <dimension ref="A1:K86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -9606,6 +9674,43 @@
         <v>10</v>
       </c>
     </row>
+    <row r="86">
+      <c r="A86" s="5" t="inlineStr">
+        <is>
+          <t>May 2026</t>
+        </is>
+      </c>
+      <c r="B86" s="5" t="n">
+        <v>2976</v>
+      </c>
+      <c r="C86" s="6" t="n">
+        <v>644</v>
+      </c>
+      <c r="D86" s="6" t="n">
+        <v>31</v>
+      </c>
+      <c r="E86" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F86" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G86" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H86" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I86" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J86" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K86" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/VIC_negative_prices.xlsx
+++ b/outputs/VIC_negative_prices.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J86"/>
+  <dimension ref="A1:J87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3406,6 +3406,40 @@
         <v>0</v>
       </c>
     </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="B87" s="3" t="n">
+        <v>11.42</v>
+      </c>
+      <c r="C87" s="3" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="D87" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E87" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F87" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G87" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H87" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I87" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J87" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3417,7 +3451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J86"/>
+  <dimension ref="A1:J87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -6374,8 +6408,42 @@
         <v>0</v>
       </c>
     </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="B87" s="3" t="n">
+        <v>11.42</v>
+      </c>
+      <c r="C87" s="3" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="D87" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E87" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F87" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G87" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H87" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I87" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J87" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="B2:B86">
+  <conditionalFormatting sqref="B2:B87">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -6387,7 +6455,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C86">
+  <conditionalFormatting sqref="C2:C87">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
@@ -6399,7 +6467,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D86">
+  <conditionalFormatting sqref="D2:D87">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
@@ -6411,7 +6479,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E86">
+  <conditionalFormatting sqref="E2:E87">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="min"/>
@@ -6423,7 +6491,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F86">
+  <conditionalFormatting sqref="F2:F87">
     <cfRule type="colorScale" priority="5">
       <colorScale>
         <cfvo type="min"/>
@@ -6435,7 +6503,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G86">
+  <conditionalFormatting sqref="G2:G87">
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="min"/>
@@ -6447,7 +6515,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H86">
+  <conditionalFormatting sqref="H2:H87">
     <cfRule type="colorScale" priority="7">
       <colorScale>
         <cfvo type="min"/>
@@ -6459,7 +6527,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I86">
+  <conditionalFormatting sqref="I2:I87">
     <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="min"/>
@@ -6471,7 +6539,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J86">
+  <conditionalFormatting sqref="J2:J87">
     <cfRule type="colorScale" priority="9">
       <colorScale>
         <cfvo type="min"/>
@@ -6493,7 +6561,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K86"/>
+  <dimension ref="A1:K87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -9711,6 +9779,43 @@
         <v>0</v>
       </c>
     </row>
+    <row r="87">
+      <c r="A87" s="5" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="B87" s="5" t="n">
+        <v>2880</v>
+      </c>
+      <c r="C87" s="6" t="n">
+        <v>329</v>
+      </c>
+      <c r="D87" s="6" t="n">
+        <v>13</v>
+      </c>
+      <c r="E87" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F87" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G87" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H87" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I87" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J87" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K87" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/VIC_negative_prices.xlsx
+++ b/outputs/VIC_negative_prices.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Percentages" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Heatmap" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Audit" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Percentages" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Heatmap" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Audit" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -523,7 +523,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>0.1</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>0.03</v>
@@ -557,7 +557,7 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>0.35</v>
+        <v>0.21</v>
       </c>
       <c r="C3" s="3" t="n">
         <v>0.1</v>
@@ -591,7 +591,7 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="C4" s="3" t="n">
         <v>0.71</v>
@@ -625,7 +625,7 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>2.82</v>
+        <v>2.52</v>
       </c>
       <c r="C5" s="3" t="n">
         <v>1.34</v>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>0.59</v>
+        <v>0.45</v>
       </c>
       <c r="C6" s="3" t="n">
         <v>0.28</v>
@@ -693,7 +693,7 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>2.99</v>
+        <v>2.89</v>
       </c>
       <c r="C7" s="3" t="n">
         <v>2.02</v>
@@ -761,31 +761,31 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>7.43</v>
+        <v>7.26</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>0.67</v>
+        <v>0.64</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>0.67</v>
+        <v>0.64</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>0.24</v>
+        <v>0.2</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>0.13</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="10">
@@ -795,16 +795,16 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>5.98</v>
+        <v>6.01</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>4.13</v>
+        <v>4.17</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>3.97</v>
+        <v>4</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>3.97</v>
+        <v>4</v>
       </c>
       <c r="F10" s="3" t="n">
         <v>2.42</v>
@@ -829,7 +829,7 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>0.86</v>
+        <v>0.83</v>
       </c>
       <c r="C11" s="3" t="n">
         <v>0.54</v>
@@ -863,7 +863,7 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>2.35</v>
+        <v>0.67</v>
       </c>
       <c r="C12" s="3" t="n">
         <v>0.24</v>
@@ -897,7 +897,7 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>5.83</v>
+        <v>4.79</v>
       </c>
       <c r="C13" s="3" t="n">
         <v>2.6</v>
@@ -931,7 +931,7 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>3.19</v>
+        <v>2.42</v>
       </c>
       <c r="C14" s="3" t="n">
         <v>1.01</v>
@@ -965,7 +965,7 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>0.35</v>
+        <v>0.21</v>
       </c>
       <c r="C15" s="3" t="n">
         <v>0.17</v>
@@ -999,7 +999,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.44</v>
       </c>
       <c r="C16" s="3" t="n">
         <v>0.24</v>
@@ -1033,16 +1033,16 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>4.27</v>
+        <v>4.23</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>3.86</v>
+        <v>3.83</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>3.7</v>
+        <v>3.66</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>3.63</v>
+        <v>3.6</v>
       </c>
       <c r="F17" s="3" t="n">
         <v>0.84</v>
@@ -1067,7 +1067,7 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>10.24</v>
+        <v>9.9</v>
       </c>
       <c r="C18" s="3" t="n">
         <v>7.81</v>
@@ -1076,7 +1076,7 @@
         <v>7.15</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>6.18</v>
+        <v>6.15</v>
       </c>
       <c r="F18" s="3" t="n">
         <v>3.37</v>
@@ -1101,19 +1101,19 @@
         </is>
       </c>
       <c r="B19" s="3" t="n">
-        <v>10.15</v>
+        <v>9.68</v>
       </c>
       <c r="C19" s="3" t="n">
-        <v>7.9</v>
+        <v>7.8</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>7.06</v>
+        <v>6.96</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>6.45</v>
+        <v>6.38</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>4.77</v>
+        <v>4.74</v>
       </c>
       <c r="G19" s="3" t="n">
         <v>0.37</v>
@@ -1135,19 +1135,19 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>8.16</v>
+        <v>8.06</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>6.25</v>
+        <v>6.22</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>5.94</v>
+        <v>5.9</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>5.28</v>
+        <v>5.24</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>2.6</v>
+        <v>2.57</v>
       </c>
       <c r="G20" s="3" t="n">
         <v>0.28</v>
@@ -1169,10 +1169,10 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>24.13</v>
+        <v>23.08</v>
       </c>
       <c r="C21" s="3" t="n">
-        <v>17.27</v>
+        <v>17.24</v>
       </c>
       <c r="D21" s="3" t="n">
         <v>15.62</v>
@@ -1203,16 +1203,16 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>26.48</v>
+        <v>26.08</v>
       </c>
       <c r="C22" s="3" t="n">
-        <v>21.54</v>
+        <v>21.64</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>19.39</v>
+        <v>19.49</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>17.71</v>
+        <v>17.81</v>
       </c>
       <c r="F22" s="3" t="n">
         <v>5.98</v>
@@ -1237,16 +1237,16 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>20.8</v>
+        <v>20.76</v>
       </c>
       <c r="C23" s="3" t="n">
         <v>16.18</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>13.28</v>
+        <v>13.32</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>12.24</v>
+        <v>12.31</v>
       </c>
       <c r="F23" s="3" t="n">
         <v>5.58</v>
@@ -1271,16 +1271,16 @@
         </is>
       </c>
       <c r="B24" s="3" t="n">
-        <v>8.74</v>
+        <v>8.6</v>
       </c>
       <c r="C24" s="3" t="n">
-        <v>5.81</v>
+        <v>5.75</v>
       </c>
       <c r="D24" s="3" t="n">
-        <v>4.17</v>
+        <v>4.1</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>2.99</v>
+        <v>2.92</v>
       </c>
       <c r="F24" s="3" t="n">
         <v>0.64</v>
@@ -1305,7 +1305,7 @@
         </is>
       </c>
       <c r="B25" s="3" t="n">
-        <v>16.08</v>
+        <v>15.73</v>
       </c>
       <c r="C25" s="3" t="n">
         <v>11.46</v>
@@ -1317,7 +1317,7 @@
         <v>7.78</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="G25" s="3" t="n">
         <v>0.76</v>
@@ -1339,7 +1339,7 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>7.39</v>
+        <v>7.36</v>
       </c>
       <c r="C26" s="3" t="n">
         <v>6.35</v>
@@ -1407,7 +1407,7 @@
         </is>
       </c>
       <c r="B28" s="3" t="n">
-        <v>14.42</v>
+        <v>14.38</v>
       </c>
       <c r="C28" s="3" t="n">
         <v>12.2</v>
@@ -1441,10 +1441,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>34.01</v>
+        <v>34.11</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>29.2</v>
+        <v>29.23</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>25.17</v>
@@ -1475,22 +1475,22 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>54.65</v>
+        <v>54.41</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>46.28</v>
+        <v>46.08</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>36.84</v>
+        <v>36.63</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>27.95</v>
+        <v>27.88</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>5.1</v>
+        <v>5.07</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>3.06</v>
+        <v>3.02</v>
       </c>
       <c r="H30" s="3" t="n">
         <v>0.87</v>
@@ -1509,7 +1509,7 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>69.42</v>
+        <v>69.59</v>
       </c>
       <c r="C31" s="3" t="n">
         <v>59.24</v>
@@ -1518,7 +1518,7 @@
         <v>50.67</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>38.64</v>
+        <v>38.71</v>
       </c>
       <c r="F31" s="3" t="n">
         <v>15.19</v>
@@ -1543,31 +1543,31 @@
         </is>
       </c>
       <c r="B32" s="3" t="n">
-        <v>30.73</v>
+        <v>30.49</v>
       </c>
       <c r="C32" s="3" t="n">
         <v>26.28</v>
       </c>
       <c r="D32" s="3" t="n">
-        <v>23.12</v>
+        <v>23.09</v>
       </c>
       <c r="E32" s="3" t="n">
         <v>19.69</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>3.82</v>
+        <v>3.75</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>1.49</v>
+        <v>1.42</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>0.66</v>
+        <v>0.59</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>0.59</v>
+        <v>0.52</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>0.52</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="33">
@@ -1577,22 +1577,22 @@
         </is>
       </c>
       <c r="B33" s="3" t="n">
-        <v>43.99</v>
+        <v>43.78</v>
       </c>
       <c r="C33" s="3" t="n">
-        <v>36.12</v>
+        <v>35.92</v>
       </c>
       <c r="D33" s="3" t="n">
-        <v>30.51</v>
+        <v>30.44</v>
       </c>
       <c r="E33" s="3" t="n">
         <v>24.63</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>10.75</v>
+        <v>10.72</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>5.44</v>
+        <v>5.48</v>
       </c>
       <c r="H33" s="3" t="n">
         <v>0.24</v>
@@ -1611,19 +1611,19 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>22.11</v>
+        <v>21.98</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>17.88</v>
+        <v>17.67</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>13.98</v>
+        <v>13.88</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>11.26</v>
+        <v>11.19</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>3.66</v>
+        <v>3.63</v>
       </c>
       <c r="G34" s="3" t="n">
         <v>1.34</v>
@@ -1645,19 +1645,19 @@
         </is>
       </c>
       <c r="B35" s="3" t="n">
-        <v>29.99</v>
+        <v>29.84</v>
       </c>
       <c r="C35" s="3" t="n">
-        <v>25.37</v>
+        <v>25.3</v>
       </c>
       <c r="D35" s="3" t="n">
-        <v>19.79</v>
+        <v>19.57</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>17.41</v>
+        <v>17.34</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>9.19</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="G35" s="3" t="n">
         <v>1</v>
@@ -1679,19 +1679,19 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>34.21</v>
+        <v>34.04</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>28.63</v>
+        <v>28.6</v>
       </c>
       <c r="D36" s="3" t="n">
         <v>20.77</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>17.34</v>
+        <v>17.37</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>12.5</v>
+        <v>12.57</v>
       </c>
       <c r="G36" s="3" t="n">
         <v>2.89</v>
@@ -1713,16 +1713,16 @@
         </is>
       </c>
       <c r="B37" s="3" t="n">
-        <v>15.83</v>
+        <v>15.76</v>
       </c>
       <c r="C37" s="3" t="n">
-        <v>14.2</v>
+        <v>14.17</v>
       </c>
       <c r="D37" s="3" t="n">
-        <v>12.22</v>
+        <v>12.19</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>10.9</v>
+        <v>10.87</v>
       </c>
       <c r="F37" s="3" t="n">
         <v>7.29</v>
@@ -1747,10 +1747,10 @@
         </is>
       </c>
       <c r="B38" s="3" t="n">
-        <v>6.18</v>
+        <v>6.25</v>
       </c>
       <c r="C38" s="3" t="n">
-        <v>5.71</v>
+        <v>5.75</v>
       </c>
       <c r="D38" s="3" t="n">
         <v>5.24</v>
@@ -1815,7 +1815,7 @@
         </is>
       </c>
       <c r="B40" s="3" t="n">
-        <v>11.53</v>
+        <v>11.49</v>
       </c>
       <c r="C40" s="3" t="n">
         <v>11.06</v>
@@ -1849,16 +1849,16 @@
         </is>
       </c>
       <c r="B41" s="3" t="n">
-        <v>24.73</v>
+        <v>24.76</v>
       </c>
       <c r="C41" s="3" t="n">
-        <v>22.68</v>
+        <v>22.75</v>
       </c>
       <c r="D41" s="3" t="n">
-        <v>19.89</v>
+        <v>19.93</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>17.91</v>
+        <v>17.98</v>
       </c>
       <c r="F41" s="3" t="n">
         <v>7.29</v>
@@ -1883,16 +1883,16 @@
         </is>
       </c>
       <c r="B42" s="3" t="n">
-        <v>30.87</v>
+        <v>30.63</v>
       </c>
       <c r="C42" s="3" t="n">
-        <v>29.06</v>
+        <v>28.99</v>
       </c>
       <c r="D42" s="3" t="n">
-        <v>25.45</v>
+        <v>25.38</v>
       </c>
       <c r="E42" s="3" t="n">
-        <v>22.88</v>
+        <v>22.81</v>
       </c>
       <c r="F42" s="3" t="n">
         <v>11.67</v>
@@ -1917,16 +1917,16 @@
         </is>
       </c>
       <c r="B43" s="3" t="n">
-        <v>39.72</v>
+        <v>39.75</v>
       </c>
       <c r="C43" s="3" t="n">
-        <v>37.03</v>
+        <v>37.06</v>
       </c>
       <c r="D43" s="3" t="n">
         <v>33.4</v>
       </c>
       <c r="E43" s="3" t="n">
-        <v>31.22</v>
+        <v>31.25</v>
       </c>
       <c r="F43" s="3" t="n">
         <v>16.63</v>
@@ -1951,31 +1951,31 @@
         </is>
       </c>
       <c r="B44" s="3" t="n">
-        <v>54.79</v>
+        <v>54.69</v>
       </c>
       <c r="C44" s="3" t="n">
-        <v>50.62</v>
+        <v>50.52</v>
       </c>
       <c r="D44" s="3" t="n">
-        <v>45.03</v>
+        <v>45</v>
       </c>
       <c r="E44" s="3" t="n">
         <v>43.02</v>
       </c>
       <c r="F44" s="3" t="n">
-        <v>24.65</v>
+        <v>24.55</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>20.14</v>
+        <v>20</v>
       </c>
       <c r="H44" s="3" t="n">
-        <v>8.609999999999999</v>
+        <v>8.58</v>
       </c>
       <c r="I44" s="3" t="n">
-        <v>3.19</v>
+        <v>3.16</v>
       </c>
       <c r="J44" s="3" t="n">
-        <v>2.15</v>
+        <v>2.12</v>
       </c>
     </row>
     <row r="45">
@@ -1985,31 +1985,31 @@
         </is>
       </c>
       <c r="B45" s="3" t="n">
-        <v>77.45</v>
+        <v>77.08</v>
       </c>
       <c r="C45" s="3" t="n">
-        <v>73.12</v>
+        <v>72.75</v>
       </c>
       <c r="D45" s="3" t="n">
-        <v>67.17</v>
+        <v>66.87</v>
       </c>
       <c r="E45" s="3" t="n">
-        <v>63.21</v>
+        <v>63.07</v>
       </c>
       <c r="F45" s="3" t="n">
-        <v>47.68</v>
+        <v>47.72</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>37</v>
+        <v>37.03</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>20.3</v>
+        <v>20.33</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>8.029999999999999</v>
+        <v>8</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>5.11</v>
+        <v>5.07</v>
       </c>
     </row>
     <row r="46">
@@ -2019,25 +2019,25 @@
         </is>
       </c>
       <c r="B46" s="3" t="n">
-        <v>56.05</v>
+        <v>55.98</v>
       </c>
       <c r="C46" s="3" t="n">
-        <v>53.12</v>
+        <v>53.09</v>
       </c>
       <c r="D46" s="3" t="n">
-        <v>50.24</v>
+        <v>50.17</v>
       </c>
       <c r="E46" s="3" t="n">
-        <v>47.48</v>
+        <v>47.41</v>
       </c>
       <c r="F46" s="3" t="n">
-        <v>35.32</v>
+        <v>35.28</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>28.93</v>
+        <v>28.83</v>
       </c>
       <c r="H46" s="3" t="n">
-        <v>10.58</v>
+        <v>10.55</v>
       </c>
       <c r="I46" s="3" t="n">
         <v>5.38</v>
@@ -2053,25 +2053,25 @@
         </is>
       </c>
       <c r="B47" s="3" t="n">
-        <v>61.31</v>
+        <v>61.27</v>
       </c>
       <c r="C47" s="3" t="n">
-        <v>58.04</v>
+        <v>58</v>
       </c>
       <c r="D47" s="3" t="n">
-        <v>53.91</v>
+        <v>53.87</v>
       </c>
       <c r="E47" s="3" t="n">
         <v>52.57</v>
       </c>
       <c r="F47" s="3" t="n">
-        <v>35.94</v>
+        <v>35.97</v>
       </c>
       <c r="G47" s="3" t="n">
-        <v>25.41</v>
+        <v>25.48</v>
       </c>
       <c r="H47" s="3" t="n">
-        <v>6.58</v>
+        <v>6.62</v>
       </c>
       <c r="I47" s="3" t="n">
         <v>3.35</v>
@@ -2087,22 +2087,22 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>52.42</v>
+        <v>52.39</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>47.92</v>
+        <v>48.02</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>41.83</v>
+        <v>41.97</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>39.68</v>
+        <v>39.78</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>31.32</v>
+        <v>31.45</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>20.26</v>
+        <v>20.36</v>
       </c>
       <c r="H48" s="3" t="n">
         <v>1.44</v>
@@ -2121,19 +2121,19 @@
         </is>
       </c>
       <c r="B49" s="3" t="n">
-        <v>30.59</v>
+        <v>30.52</v>
       </c>
       <c r="C49" s="3" t="n">
-        <v>27.01</v>
+        <v>27.08</v>
       </c>
       <c r="D49" s="3" t="n">
-        <v>21.25</v>
+        <v>21.32</v>
       </c>
       <c r="E49" s="3" t="n">
-        <v>19.41</v>
+        <v>19.48</v>
       </c>
       <c r="F49" s="3" t="n">
-        <v>13.37</v>
+        <v>13.4</v>
       </c>
       <c r="G49" s="3" t="n">
         <v>6.56</v>
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="B50" s="3" t="n">
-        <v>7.83</v>
+        <v>7.73</v>
       </c>
       <c r="C50" s="3" t="n">
         <v>6.42</v>
@@ -2189,10 +2189,10 @@
         </is>
       </c>
       <c r="B51" s="3" t="n">
-        <v>23.3</v>
+        <v>23.19</v>
       </c>
       <c r="C51" s="3" t="n">
-        <v>20.17</v>
+        <v>20.14</v>
       </c>
       <c r="D51" s="3" t="n">
         <v>16.46</v>
@@ -2223,19 +2223,19 @@
         </is>
       </c>
       <c r="B52" s="3" t="n">
-        <v>32.76</v>
+        <v>32.33</v>
       </c>
       <c r="C52" s="3" t="n">
         <v>27.96</v>
       </c>
       <c r="D52" s="3" t="n">
-        <v>22.61</v>
+        <v>22.28</v>
       </c>
       <c r="E52" s="3" t="n">
-        <v>19.39</v>
+        <v>19.46</v>
       </c>
       <c r="F52" s="3" t="n">
-        <v>15.59</v>
+        <v>15.62</v>
       </c>
       <c r="G52" s="3" t="n">
         <v>11.66</v>
@@ -2257,22 +2257,22 @@
         </is>
       </c>
       <c r="B53" s="3" t="n">
-        <v>33.9</v>
+        <v>33.7</v>
       </c>
       <c r="C53" s="3" t="n">
-        <v>28.12</v>
+        <v>28.19</v>
       </c>
       <c r="D53" s="3" t="n">
-        <v>22.98</v>
+        <v>22.78</v>
       </c>
       <c r="E53" s="3" t="n">
-        <v>20.19</v>
+        <v>20.26</v>
       </c>
       <c r="F53" s="3" t="n">
-        <v>16.63</v>
+        <v>16.7</v>
       </c>
       <c r="G53" s="3" t="n">
-        <v>10.79</v>
+        <v>10.82</v>
       </c>
       <c r="H53" s="3" t="n">
         <v>0.1</v>
@@ -2291,13 +2291,13 @@
         </is>
       </c>
       <c r="B54" s="3" t="n">
-        <v>67.08</v>
+        <v>67.19</v>
       </c>
       <c r="C54" s="3" t="n">
-        <v>62.85</v>
+        <v>62.88</v>
       </c>
       <c r="D54" s="3" t="n">
-        <v>60.52</v>
+        <v>60.49</v>
       </c>
       <c r="E54" s="3" t="n">
         <v>59.06</v>
@@ -2306,7 +2306,7 @@
         <v>57.99</v>
       </c>
       <c r="G54" s="3" t="n">
-        <v>51.84</v>
+        <v>51.91</v>
       </c>
       <c r="H54" s="3" t="n">
         <v>13.16</v>
@@ -2328,7 +2328,7 @@
         <v>64.68000000000001</v>
       </c>
       <c r="C55" s="3" t="n">
-        <v>60.42</v>
+        <v>60.55</v>
       </c>
       <c r="D55" s="3" t="n">
         <v>53.06</v>
@@ -2340,16 +2340,16 @@
         <v>48.56</v>
       </c>
       <c r="G55" s="3" t="n">
-        <v>37.16</v>
+        <v>37.33</v>
       </c>
       <c r="H55" s="3" t="n">
-        <v>9.98</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="I55" s="3" t="n">
-        <v>7.02</v>
+        <v>6.99</v>
       </c>
       <c r="J55" s="3" t="n">
-        <v>6.35</v>
+        <v>6.32</v>
       </c>
     </row>
     <row r="56">
@@ -2359,22 +2359,22 @@
         </is>
       </c>
       <c r="B56" s="3" t="n">
-        <v>63.16</v>
+        <v>63.19</v>
       </c>
       <c r="C56" s="3" t="n">
         <v>60.1</v>
       </c>
       <c r="D56" s="3" t="n">
-        <v>54.62</v>
+        <v>54.65</v>
       </c>
       <c r="E56" s="3" t="n">
-        <v>52.19</v>
+        <v>52.22</v>
       </c>
       <c r="F56" s="3" t="n">
-        <v>48.4</v>
+        <v>48.44</v>
       </c>
       <c r="G56" s="3" t="n">
-        <v>37.67</v>
+        <v>37.71</v>
       </c>
       <c r="H56" s="3" t="n">
         <v>11.01</v>
@@ -2393,31 +2393,31 @@
         </is>
       </c>
       <c r="B57" s="3" t="n">
-        <v>65.12</v>
+        <v>65.19</v>
       </c>
       <c r="C57" s="3" t="n">
-        <v>63.37</v>
+        <v>63.41</v>
       </c>
       <c r="D57" s="3" t="n">
-        <v>60.42</v>
+        <v>60.48</v>
       </c>
       <c r="E57" s="3" t="n">
-        <v>58.5</v>
+        <v>58.67</v>
       </c>
       <c r="F57" s="3" t="n">
-        <v>53.39</v>
+        <v>53.53</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>46.07</v>
+        <v>46.14</v>
       </c>
       <c r="H57" s="3" t="n">
-        <v>14.11</v>
+        <v>14.08</v>
       </c>
       <c r="I57" s="3" t="n">
         <v>12.26</v>
       </c>
       <c r="J57" s="3" t="n">
-        <v>11.36</v>
+        <v>11.32</v>
       </c>
     </row>
     <row r="58">
@@ -2433,25 +2433,25 @@
         <v>57.63</v>
       </c>
       <c r="D58" s="3" t="n">
-        <v>48.49</v>
+        <v>48.52</v>
       </c>
       <c r="E58" s="3" t="n">
-        <v>42.57</v>
+        <v>42.64</v>
       </c>
       <c r="F58" s="3" t="n">
-        <v>38.61</v>
+        <v>38.71</v>
       </c>
       <c r="G58" s="3" t="n">
-        <v>32.36</v>
+        <v>32.49</v>
       </c>
       <c r="H58" s="3" t="n">
-        <v>17</v>
+        <v>17.04</v>
       </c>
       <c r="I58" s="3" t="n">
-        <v>11.86</v>
+        <v>11.9</v>
       </c>
       <c r="J58" s="3" t="n">
-        <v>11.29</v>
+        <v>11.32</v>
       </c>
     </row>
     <row r="59">
@@ -2461,25 +2461,25 @@
         </is>
       </c>
       <c r="B59" s="3" t="n">
-        <v>61.93</v>
+        <v>61.89</v>
       </c>
       <c r="C59" s="3" t="n">
-        <v>61.17</v>
+        <v>61.21</v>
       </c>
       <c r="D59" s="3" t="n">
-        <v>55.5</v>
+        <v>55.53</v>
       </c>
       <c r="E59" s="3" t="n">
-        <v>52.08</v>
+        <v>52.16</v>
       </c>
       <c r="F59" s="3" t="n">
-        <v>50.47</v>
+        <v>50.57</v>
       </c>
       <c r="G59" s="3" t="n">
-        <v>38.4</v>
+        <v>38.51</v>
       </c>
       <c r="H59" s="3" t="n">
-        <v>16.24</v>
+        <v>16.2</v>
       </c>
       <c r="I59" s="3" t="n">
         <v>7.61</v>
@@ -2495,22 +2495,22 @@
         </is>
       </c>
       <c r="B60" s="3" t="n">
-        <v>46.03</v>
+        <v>45.93</v>
       </c>
       <c r="C60" s="3" t="n">
-        <v>44.39</v>
+        <v>44.29</v>
       </c>
       <c r="D60" s="3" t="n">
-        <v>39.25</v>
+        <v>39.15</v>
       </c>
       <c r="E60" s="3" t="n">
-        <v>35.28</v>
+        <v>35.25</v>
       </c>
       <c r="F60" s="3" t="n">
-        <v>31.18</v>
+        <v>31.22</v>
       </c>
       <c r="G60" s="3" t="n">
-        <v>15.86</v>
+        <v>15.89</v>
       </c>
       <c r="H60" s="3" t="n">
         <v>7.43</v>
@@ -2529,7 +2529,7 @@
         </is>
       </c>
       <c r="B61" s="3" t="n">
-        <v>28.75</v>
+        <v>28.72</v>
       </c>
       <c r="C61" s="3" t="n">
         <v>26.25</v>
@@ -2563,10 +2563,10 @@
         </is>
       </c>
       <c r="B62" s="3" t="n">
-        <v>12.4</v>
+        <v>12.43</v>
       </c>
       <c r="C62" s="3" t="n">
-        <v>11.26</v>
+        <v>11.29</v>
       </c>
       <c r="D62" s="3" t="n">
         <v>9.74</v>
@@ -2665,19 +2665,19 @@
         </is>
       </c>
       <c r="B65" s="3" t="n">
-        <v>41.8</v>
+        <v>41.87</v>
       </c>
       <c r="C65" s="3" t="n">
-        <v>38.78</v>
+        <v>38.81</v>
       </c>
       <c r="D65" s="3" t="n">
-        <v>35.28</v>
+        <v>35.35</v>
       </c>
       <c r="E65" s="3" t="n">
-        <v>33.17</v>
+        <v>33.2</v>
       </c>
       <c r="F65" s="3" t="n">
-        <v>21.07</v>
+        <v>21.1</v>
       </c>
       <c r="G65" s="3" t="n">
         <v>10.05</v>
@@ -2699,22 +2699,22 @@
         </is>
       </c>
       <c r="B66" s="3" t="n">
-        <v>73.16</v>
+        <v>73.12</v>
       </c>
       <c r="C66" s="3" t="n">
-        <v>64.65000000000001</v>
+        <v>64.76000000000001</v>
       </c>
       <c r="D66" s="3" t="n">
-        <v>61.6</v>
+        <v>61.74</v>
       </c>
       <c r="E66" s="3" t="n">
-        <v>57.81</v>
+        <v>57.85</v>
       </c>
       <c r="F66" s="3" t="n">
-        <v>44.69</v>
+        <v>44.83</v>
       </c>
       <c r="G66" s="3" t="n">
-        <v>21.67</v>
+        <v>21.7</v>
       </c>
       <c r="H66" s="3" t="n">
         <v>8.720000000000001</v>
@@ -2733,25 +2733,25 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>87.87</v>
+        <v>87.77</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>85.22</v>
+        <v>85.15000000000001</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>82.69</v>
+        <v>82.83</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>80.91</v>
+        <v>81.08</v>
       </c>
       <c r="F67" s="3" t="n">
         <v>63.84</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>39.45</v>
+        <v>39.52</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>23.62</v>
+        <v>23.66</v>
       </c>
       <c r="I67" s="3" t="n">
         <v>8.6</v>
@@ -2773,25 +2773,25 @@
         <v>58.33</v>
       </c>
       <c r="D68" s="3" t="n">
-        <v>54.65</v>
+        <v>54.69</v>
       </c>
       <c r="E68" s="3" t="n">
-        <v>46.7</v>
+        <v>46.74</v>
       </c>
       <c r="F68" s="3" t="n">
-        <v>29.1</v>
+        <v>29.13</v>
       </c>
       <c r="G68" s="3" t="n">
-        <v>22.05</v>
+        <v>22.08</v>
       </c>
       <c r="H68" s="3" t="n">
-        <v>16.49</v>
+        <v>16.53</v>
       </c>
       <c r="I68" s="3" t="n">
-        <v>5.94</v>
+        <v>6.01</v>
       </c>
       <c r="J68" s="3" t="n">
-        <v>5</v>
+        <v>5.07</v>
       </c>
     </row>
     <row r="69">
@@ -2801,25 +2801,25 @@
         </is>
       </c>
       <c r="B69" s="3" t="n">
-        <v>70.45999999999999</v>
+        <v>70.43000000000001</v>
       </c>
       <c r="C69" s="3" t="n">
         <v>68.72</v>
       </c>
       <c r="D69" s="3" t="n">
-        <v>64.45</v>
+        <v>64.38</v>
       </c>
       <c r="E69" s="3" t="n">
         <v>54.77</v>
       </c>
       <c r="F69" s="3" t="n">
-        <v>32.33</v>
+        <v>32.26</v>
       </c>
       <c r="G69" s="3" t="n">
-        <v>24.7</v>
+        <v>24.63</v>
       </c>
       <c r="H69" s="3" t="n">
-        <v>19.22</v>
+        <v>19.19</v>
       </c>
       <c r="I69" s="3" t="n">
         <v>6.72</v>
@@ -2835,25 +2835,25 @@
         </is>
       </c>
       <c r="B70" s="3" t="n">
-        <v>62.33</v>
+        <v>62.13</v>
       </c>
       <c r="C70" s="3" t="n">
-        <v>61.36</v>
+        <v>61.19</v>
       </c>
       <c r="D70" s="3" t="n">
-        <v>56.45</v>
+        <v>56.25</v>
       </c>
       <c r="E70" s="3" t="n">
-        <v>50.57</v>
+        <v>50.44</v>
       </c>
       <c r="F70" s="3" t="n">
-        <v>28.33</v>
+        <v>28.46</v>
       </c>
       <c r="G70" s="3" t="n">
-        <v>20.43</v>
+        <v>20.5</v>
       </c>
       <c r="H70" s="3" t="n">
-        <v>13.24</v>
+        <v>13.27</v>
       </c>
       <c r="I70" s="3" t="n">
         <v>4.81</v>
@@ -2869,22 +2869,22 @@
         </is>
       </c>
       <c r="B71" s="3" t="n">
-        <v>53.35</v>
+        <v>53.2</v>
       </c>
       <c r="C71" s="3" t="n">
-        <v>51.53</v>
+        <v>51.49</v>
       </c>
       <c r="D71" s="3" t="n">
-        <v>46.76</v>
+        <v>46.73</v>
       </c>
       <c r="E71" s="3" t="n">
         <v>36.24</v>
       </c>
       <c r="F71" s="3" t="n">
-        <v>15.89</v>
+        <v>15.92</v>
       </c>
       <c r="G71" s="3" t="n">
-        <v>8.67</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="H71" s="3" t="n">
         <v>4.72</v>
@@ -2903,25 +2903,25 @@
         </is>
       </c>
       <c r="B72" s="3" t="n">
-        <v>40.83</v>
+        <v>40.66</v>
       </c>
       <c r="C72" s="3" t="n">
-        <v>35.42</v>
+        <v>35.45</v>
       </c>
       <c r="D72" s="3" t="n">
-        <v>28.46</v>
+        <v>28.53</v>
       </c>
       <c r="E72" s="3" t="n">
-        <v>11.42</v>
+        <v>11.46</v>
       </c>
       <c r="F72" s="3" t="n">
-        <v>5.51</v>
+        <v>5.58</v>
       </c>
       <c r="G72" s="3" t="n">
-        <v>3.33</v>
+        <v>3.36</v>
       </c>
       <c r="H72" s="3" t="n">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="I72" s="3" t="n">
         <v>0.44</v>
@@ -2937,13 +2937,13 @@
         </is>
       </c>
       <c r="B73" s="3" t="n">
-        <v>40.83</v>
+        <v>40.62</v>
       </c>
       <c r="C73" s="3" t="n">
-        <v>36.08</v>
+        <v>36.11</v>
       </c>
       <c r="D73" s="3" t="n">
-        <v>30.45</v>
+        <v>30.52</v>
       </c>
       <c r="E73" s="3" t="n">
         <v>8.92</v>
@@ -2971,13 +2971,13 @@
         </is>
       </c>
       <c r="B74" s="3" t="n">
-        <v>30.51</v>
+        <v>30.41</v>
       </c>
       <c r="C74" s="3" t="n">
-        <v>28.56</v>
+        <v>28.76</v>
       </c>
       <c r="D74" s="3" t="n">
-        <v>18.68</v>
+        <v>18.62</v>
       </c>
       <c r="E74" s="3" t="n">
         <v>5.51</v>
@@ -3005,7 +3005,7 @@
         </is>
       </c>
       <c r="B75" s="3" t="n">
-        <v>6.39</v>
+        <v>6.28</v>
       </c>
       <c r="C75" s="3" t="n">
         <v>5.24</v>
@@ -3073,10 +3073,10 @@
         </is>
       </c>
       <c r="B77" s="3" t="n">
-        <v>24.06</v>
+        <v>23.92</v>
       </c>
       <c r="C77" s="3" t="n">
-        <v>14.72</v>
+        <v>14.75</v>
       </c>
       <c r="D77" s="3" t="n">
         <v>0.67</v>
@@ -3107,16 +3107,16 @@
         </is>
       </c>
       <c r="B78" s="3" t="n">
-        <v>66.67</v>
+        <v>66.73999999999999</v>
       </c>
       <c r="C78" s="3" t="n">
-        <v>45.83</v>
+        <v>46.01</v>
       </c>
       <c r="D78" s="3" t="n">
-        <v>17.88</v>
+        <v>17.95</v>
       </c>
       <c r="E78" s="3" t="n">
-        <v>8.44</v>
+        <v>8.51</v>
       </c>
       <c r="F78" s="3" t="n">
         <v>6.7</v>
@@ -3141,25 +3141,25 @@
         </is>
       </c>
       <c r="B79" s="3" t="n">
-        <v>70.40000000000001</v>
+        <v>70.36</v>
       </c>
       <c r="C79" s="3" t="n">
-        <v>57.66</v>
+        <v>57.83</v>
       </c>
       <c r="D79" s="3" t="n">
-        <v>27.08</v>
+        <v>27.15</v>
       </c>
       <c r="E79" s="3" t="n">
-        <v>15.32</v>
+        <v>15.36</v>
       </c>
       <c r="F79" s="3" t="n">
-        <v>8.74</v>
+        <v>8.77</v>
       </c>
       <c r="G79" s="3" t="n">
-        <v>7.39</v>
+        <v>7.43</v>
       </c>
       <c r="H79" s="3" t="n">
-        <v>1.88</v>
+        <v>1.92</v>
       </c>
       <c r="I79" s="3" t="n">
         <v>0.3</v>
@@ -3175,13 +3175,13 @@
         </is>
       </c>
       <c r="B80" s="3" t="n">
-        <v>88.3</v>
+        <v>88.06</v>
       </c>
       <c r="C80" s="3" t="n">
-        <v>70.09999999999999</v>
+        <v>70.20999999999999</v>
       </c>
       <c r="D80" s="3" t="n">
-        <v>28.85</v>
+        <v>28.92</v>
       </c>
       <c r="E80" s="3" t="n">
         <v>16.81</v>
@@ -3209,31 +3209,31 @@
         </is>
       </c>
       <c r="B81" s="3" t="n">
-        <v>71.27</v>
+        <v>70.97</v>
       </c>
       <c r="C81" s="3" t="n">
         <v>50.67</v>
       </c>
       <c r="D81" s="3" t="n">
-        <v>34.78</v>
+        <v>34.81</v>
       </c>
       <c r="E81" s="3" t="n">
-        <v>28.7</v>
+        <v>28.8</v>
       </c>
       <c r="F81" s="3" t="n">
-        <v>25.24</v>
+        <v>25.37</v>
       </c>
       <c r="G81" s="3" t="n">
-        <v>23.79</v>
+        <v>23.92</v>
       </c>
       <c r="H81" s="3" t="n">
-        <v>13.41</v>
+        <v>13.51</v>
       </c>
       <c r="I81" s="3" t="n">
-        <v>7.93</v>
+        <v>7.96</v>
       </c>
       <c r="J81" s="3" t="n">
-        <v>7.46</v>
+        <v>7.49</v>
       </c>
     </row>
     <row r="82">
@@ -3243,25 +3243,25 @@
         </is>
       </c>
       <c r="B82" s="3" t="n">
-        <v>53.97</v>
+        <v>53.8</v>
       </c>
       <c r="C82" s="3" t="n">
-        <v>28.53</v>
+        <v>28.43</v>
       </c>
       <c r="D82" s="3" t="n">
-        <v>16.4</v>
+        <v>16.47</v>
       </c>
       <c r="E82" s="3" t="n">
-        <v>12.03</v>
+        <v>12.1</v>
       </c>
       <c r="F82" s="3" t="n">
-        <v>9.91</v>
+        <v>9.98</v>
       </c>
       <c r="G82" s="3" t="n">
-        <v>8.300000000000001</v>
+        <v>8.33</v>
       </c>
       <c r="H82" s="3" t="n">
-        <v>6.15</v>
+        <v>6.22</v>
       </c>
       <c r="I82" s="3" t="n">
         <v>2.99</v>
@@ -3277,16 +3277,16 @@
         </is>
       </c>
       <c r="B83" s="3" t="n">
-        <v>48.14</v>
+        <v>48.1</v>
       </c>
       <c r="C83" s="3" t="n">
-        <v>15.1</v>
+        <v>15.14</v>
       </c>
       <c r="D83" s="3" t="n">
-        <v>7.92</v>
+        <v>7.96</v>
       </c>
       <c r="E83" s="3" t="n">
-        <v>4.17</v>
+        <v>4.2</v>
       </c>
       <c r="F83" s="3" t="n">
         <v>2.01</v>
@@ -3311,25 +3311,25 @@
         </is>
       </c>
       <c r="B84" s="3" t="n">
-        <v>54.13</v>
+        <v>54.2</v>
       </c>
       <c r="C84" s="3" t="n">
-        <v>25.1</v>
+        <v>25.2</v>
       </c>
       <c r="D84" s="3" t="n">
-        <v>12.77</v>
+        <v>12.84</v>
       </c>
       <c r="E84" s="3" t="n">
-        <v>10.35</v>
+        <v>10.42</v>
       </c>
       <c r="F84" s="3" t="n">
-        <v>4.94</v>
+        <v>4.97</v>
       </c>
       <c r="G84" s="3" t="n">
-        <v>3.46</v>
+        <v>3.49</v>
       </c>
       <c r="H84" s="3" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="I84" s="3" t="n">
         <v>0.03</v>
@@ -3345,19 +3345,19 @@
         </is>
       </c>
       <c r="B85" s="3" t="n">
-        <v>56.49</v>
+        <v>56.35</v>
       </c>
       <c r="C85" s="3" t="n">
-        <v>21.25</v>
+        <v>21.35</v>
       </c>
       <c r="D85" s="3" t="n">
-        <v>10.24</v>
+        <v>10.31</v>
       </c>
       <c r="E85" s="3" t="n">
-        <v>7.81</v>
+        <v>7.85</v>
       </c>
       <c r="F85" s="3" t="n">
-        <v>5.97</v>
+        <v>6.01</v>
       </c>
       <c r="G85" s="3" t="n">
         <v>4.62</v>
@@ -3379,10 +3379,10 @@
         </is>
       </c>
       <c r="B86" s="3" t="n">
-        <v>21.64</v>
+        <v>21.4</v>
       </c>
       <c r="C86" s="3" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="D86" s="3" t="n">
         <v>0.03</v>
@@ -3447,7 +3447,7 @@
         </is>
       </c>
       <c r="B88" s="3" t="n">
-        <v>14.35</v>
+        <v>14.11</v>
       </c>
       <c r="C88" s="3" t="n">
         <v>1.24</v>
@@ -3481,7 +3481,7 @@
         </is>
       </c>
       <c r="B89" s="3" t="n">
-        <v>22.55</v>
+        <v>22.51</v>
       </c>
       <c r="C89" s="3" t="n">
         <v>3.26</v>
@@ -3593,7 +3593,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>0.1</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>0.03</v>
@@ -3627,7 +3627,7 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>0.35</v>
+        <v>0.21</v>
       </c>
       <c r="C3" s="3" t="n">
         <v>0.1</v>
@@ -3661,7 +3661,7 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="C4" s="3" t="n">
         <v>0.71</v>
@@ -3695,7 +3695,7 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>2.82</v>
+        <v>2.52</v>
       </c>
       <c r="C5" s="3" t="n">
         <v>1.34</v>
@@ -3729,7 +3729,7 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>0.59</v>
+        <v>0.45</v>
       </c>
       <c r="C6" s="3" t="n">
         <v>0.28</v>
@@ -3763,7 +3763,7 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>2.99</v>
+        <v>2.89</v>
       </c>
       <c r="C7" s="3" t="n">
         <v>2.02</v>
@@ -3831,31 +3831,31 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>7.43</v>
+        <v>7.26</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>0.67</v>
+        <v>0.64</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>0.67</v>
+        <v>0.64</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>0.24</v>
+        <v>0.2</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>0.13</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="10">
@@ -3865,16 +3865,16 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>5.98</v>
+        <v>6.01</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>4.13</v>
+        <v>4.17</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>3.97</v>
+        <v>4</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>3.97</v>
+        <v>4</v>
       </c>
       <c r="F10" s="3" t="n">
         <v>2.42</v>
@@ -3899,7 +3899,7 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>0.86</v>
+        <v>0.83</v>
       </c>
       <c r="C11" s="3" t="n">
         <v>0.54</v>
@@ -3933,7 +3933,7 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>2.35</v>
+        <v>0.67</v>
       </c>
       <c r="C12" s="3" t="n">
         <v>0.24</v>
@@ -3967,7 +3967,7 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>5.83</v>
+        <v>4.79</v>
       </c>
       <c r="C13" s="3" t="n">
         <v>2.6</v>
@@ -4001,7 +4001,7 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>3.19</v>
+        <v>2.42</v>
       </c>
       <c r="C14" s="3" t="n">
         <v>1.01</v>
@@ -4035,7 +4035,7 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>0.35</v>
+        <v>0.21</v>
       </c>
       <c r="C15" s="3" t="n">
         <v>0.17</v>
@@ -4069,7 +4069,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.44</v>
       </c>
       <c r="C16" s="3" t="n">
         <v>0.24</v>
@@ -4103,16 +4103,16 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>4.27</v>
+        <v>4.23</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>3.86</v>
+        <v>3.83</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>3.7</v>
+        <v>3.66</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>3.63</v>
+        <v>3.6</v>
       </c>
       <c r="F17" s="3" t="n">
         <v>0.84</v>
@@ -4137,7 +4137,7 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>10.24</v>
+        <v>9.9</v>
       </c>
       <c r="C18" s="3" t="n">
         <v>7.81</v>
@@ -4146,7 +4146,7 @@
         <v>7.15</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>6.18</v>
+        <v>6.15</v>
       </c>
       <c r="F18" s="3" t="n">
         <v>3.37</v>
@@ -4171,19 +4171,19 @@
         </is>
       </c>
       <c r="B19" s="3" t="n">
-        <v>10.15</v>
+        <v>9.68</v>
       </c>
       <c r="C19" s="3" t="n">
-        <v>7.9</v>
+        <v>7.8</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>7.06</v>
+        <v>6.96</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>6.45</v>
+        <v>6.38</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>4.77</v>
+        <v>4.74</v>
       </c>
       <c r="G19" s="3" t="n">
         <v>0.37</v>
@@ -4205,19 +4205,19 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>8.16</v>
+        <v>8.06</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>6.25</v>
+        <v>6.22</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>5.94</v>
+        <v>5.9</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>5.28</v>
+        <v>5.24</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>2.6</v>
+        <v>2.57</v>
       </c>
       <c r="G20" s="3" t="n">
         <v>0.28</v>
@@ -4239,10 +4239,10 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>24.13</v>
+        <v>23.08</v>
       </c>
       <c r="C21" s="3" t="n">
-        <v>17.27</v>
+        <v>17.24</v>
       </c>
       <c r="D21" s="3" t="n">
         <v>15.62</v>
@@ -4273,16 +4273,16 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>26.48</v>
+        <v>26.08</v>
       </c>
       <c r="C22" s="3" t="n">
-        <v>21.54</v>
+        <v>21.64</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>19.39</v>
+        <v>19.49</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>17.71</v>
+        <v>17.81</v>
       </c>
       <c r="F22" s="3" t="n">
         <v>5.98</v>
@@ -4307,16 +4307,16 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>20.8</v>
+        <v>20.76</v>
       </c>
       <c r="C23" s="3" t="n">
         <v>16.18</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>13.28</v>
+        <v>13.32</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>12.24</v>
+        <v>12.31</v>
       </c>
       <c r="F23" s="3" t="n">
         <v>5.58</v>
@@ -4341,16 +4341,16 @@
         </is>
       </c>
       <c r="B24" s="3" t="n">
-        <v>8.74</v>
+        <v>8.6</v>
       </c>
       <c r="C24" s="3" t="n">
-        <v>5.81</v>
+        <v>5.75</v>
       </c>
       <c r="D24" s="3" t="n">
-        <v>4.17</v>
+        <v>4.1</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>2.99</v>
+        <v>2.92</v>
       </c>
       <c r="F24" s="3" t="n">
         <v>0.64</v>
@@ -4375,7 +4375,7 @@
         </is>
       </c>
       <c r="B25" s="3" t="n">
-        <v>16.08</v>
+        <v>15.73</v>
       </c>
       <c r="C25" s="3" t="n">
         <v>11.46</v>
@@ -4387,7 +4387,7 @@
         <v>7.78</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="G25" s="3" t="n">
         <v>0.76</v>
@@ -4409,7 +4409,7 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>7.39</v>
+        <v>7.36</v>
       </c>
       <c r="C26" s="3" t="n">
         <v>6.35</v>
@@ -4477,7 +4477,7 @@
         </is>
       </c>
       <c r="B28" s="3" t="n">
-        <v>14.42</v>
+        <v>14.38</v>
       </c>
       <c r="C28" s="3" t="n">
         <v>12.2</v>
@@ -4511,10 +4511,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>34.01</v>
+        <v>34.11</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>29.2</v>
+        <v>29.23</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>25.17</v>
@@ -4545,22 +4545,22 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>54.65</v>
+        <v>54.41</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>46.28</v>
+        <v>46.08</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>36.84</v>
+        <v>36.63</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>27.95</v>
+        <v>27.88</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>5.1</v>
+        <v>5.07</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>3.06</v>
+        <v>3.02</v>
       </c>
       <c r="H30" s="3" t="n">
         <v>0.87</v>
@@ -4579,7 +4579,7 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>69.42</v>
+        <v>69.59</v>
       </c>
       <c r="C31" s="3" t="n">
         <v>59.24</v>
@@ -4588,7 +4588,7 @@
         <v>50.67</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>38.64</v>
+        <v>38.71</v>
       </c>
       <c r="F31" s="3" t="n">
         <v>15.19</v>
@@ -4613,31 +4613,31 @@
         </is>
       </c>
       <c r="B32" s="3" t="n">
-        <v>30.73</v>
+        <v>30.49</v>
       </c>
       <c r="C32" s="3" t="n">
         <v>26.28</v>
       </c>
       <c r="D32" s="3" t="n">
-        <v>23.12</v>
+        <v>23.09</v>
       </c>
       <c r="E32" s="3" t="n">
         <v>19.69</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>3.82</v>
+        <v>3.75</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>1.49</v>
+        <v>1.42</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>0.66</v>
+        <v>0.59</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>0.59</v>
+        <v>0.52</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>0.52</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="33">
@@ -4647,22 +4647,22 @@
         </is>
       </c>
       <c r="B33" s="3" t="n">
-        <v>43.99</v>
+        <v>43.78</v>
       </c>
       <c r="C33" s="3" t="n">
-        <v>36.12</v>
+        <v>35.92</v>
       </c>
       <c r="D33" s="3" t="n">
-        <v>30.51</v>
+        <v>30.44</v>
       </c>
       <c r="E33" s="3" t="n">
         <v>24.63</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>10.75</v>
+        <v>10.72</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>5.44</v>
+        <v>5.48</v>
       </c>
       <c r="H33" s="3" t="n">
         <v>0.24</v>
@@ -4681,19 +4681,19 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>22.11</v>
+        <v>21.98</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>17.88</v>
+        <v>17.67</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>13.98</v>
+        <v>13.88</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>11.26</v>
+        <v>11.19</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>3.66</v>
+        <v>3.63</v>
       </c>
       <c r="G34" s="3" t="n">
         <v>1.34</v>
@@ -4715,19 +4715,19 @@
         </is>
       </c>
       <c r="B35" s="3" t="n">
-        <v>29.99</v>
+        <v>29.84</v>
       </c>
       <c r="C35" s="3" t="n">
-        <v>25.37</v>
+        <v>25.3</v>
       </c>
       <c r="D35" s="3" t="n">
-        <v>19.79</v>
+        <v>19.57</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>17.41</v>
+        <v>17.34</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>9.19</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="G35" s="3" t="n">
         <v>1</v>
@@ -4749,19 +4749,19 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>34.21</v>
+        <v>34.04</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>28.63</v>
+        <v>28.6</v>
       </c>
       <c r="D36" s="3" t="n">
         <v>20.77</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>17.34</v>
+        <v>17.37</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>12.5</v>
+        <v>12.57</v>
       </c>
       <c r="G36" s="3" t="n">
         <v>2.89</v>
@@ -4783,16 +4783,16 @@
         </is>
       </c>
       <c r="B37" s="3" t="n">
-        <v>15.83</v>
+        <v>15.76</v>
       </c>
       <c r="C37" s="3" t="n">
-        <v>14.2</v>
+        <v>14.17</v>
       </c>
       <c r="D37" s="3" t="n">
-        <v>12.22</v>
+        <v>12.19</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>10.9</v>
+        <v>10.87</v>
       </c>
       <c r="F37" s="3" t="n">
         <v>7.29</v>
@@ -4817,10 +4817,10 @@
         </is>
       </c>
       <c r="B38" s="3" t="n">
-        <v>6.18</v>
+        <v>6.25</v>
       </c>
       <c r="C38" s="3" t="n">
-        <v>5.71</v>
+        <v>5.75</v>
       </c>
       <c r="D38" s="3" t="n">
         <v>5.24</v>
@@ -4885,7 +4885,7 @@
         </is>
       </c>
       <c r="B40" s="3" t="n">
-        <v>11.53</v>
+        <v>11.49</v>
       </c>
       <c r="C40" s="3" t="n">
         <v>11.06</v>
@@ -4919,16 +4919,16 @@
         </is>
       </c>
       <c r="B41" s="3" t="n">
-        <v>24.73</v>
+        <v>24.76</v>
       </c>
       <c r="C41" s="3" t="n">
-        <v>22.68</v>
+        <v>22.75</v>
       </c>
       <c r="D41" s="3" t="n">
-        <v>19.89</v>
+        <v>19.93</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>17.91</v>
+        <v>17.98</v>
       </c>
       <c r="F41" s="3" t="n">
         <v>7.29</v>
@@ -4953,16 +4953,16 @@
         </is>
       </c>
       <c r="B42" s="3" t="n">
-        <v>30.87</v>
+        <v>30.63</v>
       </c>
       <c r="C42" s="3" t="n">
-        <v>29.06</v>
+        <v>28.99</v>
       </c>
       <c r="D42" s="3" t="n">
-        <v>25.45</v>
+        <v>25.38</v>
       </c>
       <c r="E42" s="3" t="n">
-        <v>22.88</v>
+        <v>22.81</v>
       </c>
       <c r="F42" s="3" t="n">
         <v>11.67</v>
@@ -4987,16 +4987,16 @@
         </is>
       </c>
       <c r="B43" s="3" t="n">
-        <v>39.72</v>
+        <v>39.75</v>
       </c>
       <c r="C43" s="3" t="n">
-        <v>37.03</v>
+        <v>37.06</v>
       </c>
       <c r="D43" s="3" t="n">
         <v>33.4</v>
       </c>
       <c r="E43" s="3" t="n">
-        <v>31.22</v>
+        <v>31.25</v>
       </c>
       <c r="F43" s="3" t="n">
         <v>16.63</v>
@@ -5021,31 +5021,31 @@
         </is>
       </c>
       <c r="B44" s="3" t="n">
-        <v>54.79</v>
+        <v>54.69</v>
       </c>
       <c r="C44" s="3" t="n">
-        <v>50.62</v>
+        <v>50.52</v>
       </c>
       <c r="D44" s="3" t="n">
-        <v>45.03</v>
+        <v>45</v>
       </c>
       <c r="E44" s="3" t="n">
         <v>43.02</v>
       </c>
       <c r="F44" s="3" t="n">
-        <v>24.65</v>
+        <v>24.55</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>20.14</v>
+        <v>20</v>
       </c>
       <c r="H44" s="3" t="n">
-        <v>8.609999999999999</v>
+        <v>8.58</v>
       </c>
       <c r="I44" s="3" t="n">
-        <v>3.19</v>
+        <v>3.16</v>
       </c>
       <c r="J44" s="3" t="n">
-        <v>2.15</v>
+        <v>2.12</v>
       </c>
     </row>
     <row r="45">
@@ -5055,31 +5055,31 @@
         </is>
       </c>
       <c r="B45" s="3" t="n">
-        <v>77.45</v>
+        <v>77.08</v>
       </c>
       <c r="C45" s="3" t="n">
-        <v>73.12</v>
+        <v>72.75</v>
       </c>
       <c r="D45" s="3" t="n">
-        <v>67.17</v>
+        <v>66.87</v>
       </c>
       <c r="E45" s="3" t="n">
-        <v>63.21</v>
+        <v>63.07</v>
       </c>
       <c r="F45" s="3" t="n">
-        <v>47.68</v>
+        <v>47.72</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>37</v>
+        <v>37.03</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>20.3</v>
+        <v>20.33</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>8.029999999999999</v>
+        <v>8</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>5.11</v>
+        <v>5.07</v>
       </c>
     </row>
     <row r="46">
@@ -5089,25 +5089,25 @@
         </is>
       </c>
       <c r="B46" s="3" t="n">
-        <v>56.05</v>
+        <v>55.98</v>
       </c>
       <c r="C46" s="3" t="n">
-        <v>53.12</v>
+        <v>53.09</v>
       </c>
       <c r="D46" s="3" t="n">
-        <v>50.24</v>
+        <v>50.17</v>
       </c>
       <c r="E46" s="3" t="n">
-        <v>47.48</v>
+        <v>47.41</v>
       </c>
       <c r="F46" s="3" t="n">
-        <v>35.32</v>
+        <v>35.28</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>28.93</v>
+        <v>28.83</v>
       </c>
       <c r="H46" s="3" t="n">
-        <v>10.58</v>
+        <v>10.55</v>
       </c>
       <c r="I46" s="3" t="n">
         <v>5.38</v>
@@ -5123,25 +5123,25 @@
         </is>
       </c>
       <c r="B47" s="3" t="n">
-        <v>61.31</v>
+        <v>61.27</v>
       </c>
       <c r="C47" s="3" t="n">
-        <v>58.04</v>
+        <v>58</v>
       </c>
       <c r="D47" s="3" t="n">
-        <v>53.91</v>
+        <v>53.87</v>
       </c>
       <c r="E47" s="3" t="n">
         <v>52.57</v>
       </c>
       <c r="F47" s="3" t="n">
-        <v>35.94</v>
+        <v>35.97</v>
       </c>
       <c r="G47" s="3" t="n">
-        <v>25.41</v>
+        <v>25.48</v>
       </c>
       <c r="H47" s="3" t="n">
-        <v>6.58</v>
+        <v>6.62</v>
       </c>
       <c r="I47" s="3" t="n">
         <v>3.35</v>
@@ -5157,22 +5157,22 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>52.42</v>
+        <v>52.39</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>47.92</v>
+        <v>48.02</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>41.83</v>
+        <v>41.97</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>39.68</v>
+        <v>39.78</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>31.32</v>
+        <v>31.45</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>20.26</v>
+        <v>20.36</v>
       </c>
       <c r="H48" s="3" t="n">
         <v>1.44</v>
@@ -5191,19 +5191,19 @@
         </is>
       </c>
       <c r="B49" s="3" t="n">
-        <v>30.59</v>
+        <v>30.52</v>
       </c>
       <c r="C49" s="3" t="n">
-        <v>27.01</v>
+        <v>27.08</v>
       </c>
       <c r="D49" s="3" t="n">
-        <v>21.25</v>
+        <v>21.32</v>
       </c>
       <c r="E49" s="3" t="n">
-        <v>19.41</v>
+        <v>19.48</v>
       </c>
       <c r="F49" s="3" t="n">
-        <v>13.37</v>
+        <v>13.4</v>
       </c>
       <c r="G49" s="3" t="n">
         <v>6.56</v>
@@ -5225,7 +5225,7 @@
         </is>
       </c>
       <c r="B50" s="3" t="n">
-        <v>7.83</v>
+        <v>7.73</v>
       </c>
       <c r="C50" s="3" t="n">
         <v>6.42</v>
@@ -5259,10 +5259,10 @@
         </is>
       </c>
       <c r="B51" s="3" t="n">
-        <v>23.3</v>
+        <v>23.19</v>
       </c>
       <c r="C51" s="3" t="n">
-        <v>20.17</v>
+        <v>20.14</v>
       </c>
       <c r="D51" s="3" t="n">
         <v>16.46</v>
@@ -5293,19 +5293,19 @@
         </is>
       </c>
       <c r="B52" s="3" t="n">
-        <v>32.76</v>
+        <v>32.33</v>
       </c>
       <c r="C52" s="3" t="n">
         <v>27.96</v>
       </c>
       <c r="D52" s="3" t="n">
-        <v>22.61</v>
+        <v>22.28</v>
       </c>
       <c r="E52" s="3" t="n">
-        <v>19.39</v>
+        <v>19.46</v>
       </c>
       <c r="F52" s="3" t="n">
-        <v>15.59</v>
+        <v>15.62</v>
       </c>
       <c r="G52" s="3" t="n">
         <v>11.66</v>
@@ -5327,22 +5327,22 @@
         </is>
       </c>
       <c r="B53" s="3" t="n">
-        <v>33.9</v>
+        <v>33.7</v>
       </c>
       <c r="C53" s="3" t="n">
-        <v>28.12</v>
+        <v>28.19</v>
       </c>
       <c r="D53" s="3" t="n">
-        <v>22.98</v>
+        <v>22.78</v>
       </c>
       <c r="E53" s="3" t="n">
-        <v>20.19</v>
+        <v>20.26</v>
       </c>
       <c r="F53" s="3" t="n">
-        <v>16.63</v>
+        <v>16.7</v>
       </c>
       <c r="G53" s="3" t="n">
-        <v>10.79</v>
+        <v>10.82</v>
       </c>
       <c r="H53" s="3" t="n">
         <v>0.1</v>
@@ -5361,13 +5361,13 @@
         </is>
       </c>
       <c r="B54" s="3" t="n">
-        <v>67.08</v>
+        <v>67.19</v>
       </c>
       <c r="C54" s="3" t="n">
-        <v>62.85</v>
+        <v>62.88</v>
       </c>
       <c r="D54" s="3" t="n">
-        <v>60.52</v>
+        <v>60.49</v>
       </c>
       <c r="E54" s="3" t="n">
         <v>59.06</v>
@@ -5376,7 +5376,7 @@
         <v>57.99</v>
       </c>
       <c r="G54" s="3" t="n">
-        <v>51.84</v>
+        <v>51.91</v>
       </c>
       <c r="H54" s="3" t="n">
         <v>13.16</v>
@@ -5398,7 +5398,7 @@
         <v>64.68000000000001</v>
       </c>
       <c r="C55" s="3" t="n">
-        <v>60.42</v>
+        <v>60.55</v>
       </c>
       <c r="D55" s="3" t="n">
         <v>53.06</v>
@@ -5410,16 +5410,16 @@
         <v>48.56</v>
       </c>
       <c r="G55" s="3" t="n">
-        <v>37.16</v>
+        <v>37.33</v>
       </c>
       <c r="H55" s="3" t="n">
-        <v>9.98</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="I55" s="3" t="n">
-        <v>7.02</v>
+        <v>6.99</v>
       </c>
       <c r="J55" s="3" t="n">
-        <v>6.35</v>
+        <v>6.32</v>
       </c>
     </row>
     <row r="56">
@@ -5429,22 +5429,22 @@
         </is>
       </c>
       <c r="B56" s="3" t="n">
-        <v>63.16</v>
+        <v>63.19</v>
       </c>
       <c r="C56" s="3" t="n">
         <v>60.1</v>
       </c>
       <c r="D56" s="3" t="n">
-        <v>54.62</v>
+        <v>54.65</v>
       </c>
       <c r="E56" s="3" t="n">
-        <v>52.19</v>
+        <v>52.22</v>
       </c>
       <c r="F56" s="3" t="n">
-        <v>48.4</v>
+        <v>48.44</v>
       </c>
       <c r="G56" s="3" t="n">
-        <v>37.67</v>
+        <v>37.71</v>
       </c>
       <c r="H56" s="3" t="n">
         <v>11.01</v>
@@ -5463,31 +5463,31 @@
         </is>
       </c>
       <c r="B57" s="3" t="n">
-        <v>65.12</v>
+        <v>65.19</v>
       </c>
       <c r="C57" s="3" t="n">
-        <v>63.37</v>
+        <v>63.41</v>
       </c>
       <c r="D57" s="3" t="n">
-        <v>60.42</v>
+        <v>60.48</v>
       </c>
       <c r="E57" s="3" t="n">
-        <v>58.5</v>
+        <v>58.67</v>
       </c>
       <c r="F57" s="3" t="n">
-        <v>53.39</v>
+        <v>53.53</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>46.07</v>
+        <v>46.14</v>
       </c>
       <c r="H57" s="3" t="n">
-        <v>14.11</v>
+        <v>14.08</v>
       </c>
       <c r="I57" s="3" t="n">
         <v>12.26</v>
       </c>
       <c r="J57" s="3" t="n">
-        <v>11.36</v>
+        <v>11.32</v>
       </c>
     </row>
     <row r="58">
@@ -5503,25 +5503,25 @@
         <v>57.63</v>
       </c>
       <c r="D58" s="3" t="n">
-        <v>48.49</v>
+        <v>48.52</v>
       </c>
       <c r="E58" s="3" t="n">
-        <v>42.57</v>
+        <v>42.64</v>
       </c>
       <c r="F58" s="3" t="n">
-        <v>38.61</v>
+        <v>38.71</v>
       </c>
       <c r="G58" s="3" t="n">
-        <v>32.36</v>
+        <v>32.49</v>
       </c>
       <c r="H58" s="3" t="n">
-        <v>17</v>
+        <v>17.04</v>
       </c>
       <c r="I58" s="3" t="n">
-        <v>11.86</v>
+        <v>11.9</v>
       </c>
       <c r="J58" s="3" t="n">
-        <v>11.29</v>
+        <v>11.32</v>
       </c>
     </row>
     <row r="59">
@@ -5531,25 +5531,25 @@
         </is>
       </c>
       <c r="B59" s="3" t="n">
-        <v>61.93</v>
+        <v>61.89</v>
       </c>
       <c r="C59" s="3" t="n">
-        <v>61.17</v>
+        <v>61.21</v>
       </c>
       <c r="D59" s="3" t="n">
-        <v>55.5</v>
+        <v>55.53</v>
       </c>
       <c r="E59" s="3" t="n">
-        <v>52.08</v>
+        <v>52.16</v>
       </c>
       <c r="F59" s="3" t="n">
-        <v>50.47</v>
+        <v>50.57</v>
       </c>
       <c r="G59" s="3" t="n">
-        <v>38.4</v>
+        <v>38.51</v>
       </c>
       <c r="H59" s="3" t="n">
-        <v>16.24</v>
+        <v>16.2</v>
       </c>
       <c r="I59" s="3" t="n">
         <v>7.61</v>
@@ -5565,22 +5565,22 @@
         </is>
       </c>
       <c r="B60" s="3" t="n">
-        <v>46.03</v>
+        <v>45.93</v>
       </c>
       <c r="C60" s="3" t="n">
-        <v>44.39</v>
+        <v>44.29</v>
       </c>
       <c r="D60" s="3" t="n">
-        <v>39.25</v>
+        <v>39.15</v>
       </c>
       <c r="E60" s="3" t="n">
-        <v>35.28</v>
+        <v>35.25</v>
       </c>
       <c r="F60" s="3" t="n">
-        <v>31.18</v>
+        <v>31.22</v>
       </c>
       <c r="G60" s="3" t="n">
-        <v>15.86</v>
+        <v>15.89</v>
       </c>
       <c r="H60" s="3" t="n">
         <v>7.43</v>
@@ -5599,7 +5599,7 @@
         </is>
       </c>
       <c r="B61" s="3" t="n">
-        <v>28.75</v>
+        <v>28.72</v>
       </c>
       <c r="C61" s="3" t="n">
         <v>26.25</v>
@@ -5633,10 +5633,10 @@
         </is>
       </c>
       <c r="B62" s="3" t="n">
-        <v>12.4</v>
+        <v>12.43</v>
       </c>
       <c r="C62" s="3" t="n">
-        <v>11.26</v>
+        <v>11.29</v>
       </c>
       <c r="D62" s="3" t="n">
         <v>9.74</v>
@@ -5735,19 +5735,19 @@
         </is>
       </c>
       <c r="B65" s="3" t="n">
-        <v>41.8</v>
+        <v>41.87</v>
       </c>
       <c r="C65" s="3" t="n">
-        <v>38.78</v>
+        <v>38.81</v>
       </c>
       <c r="D65" s="3" t="n">
-        <v>35.28</v>
+        <v>35.35</v>
       </c>
       <c r="E65" s="3" t="n">
-        <v>33.17</v>
+        <v>33.2</v>
       </c>
       <c r="F65" s="3" t="n">
-        <v>21.07</v>
+        <v>21.1</v>
       </c>
       <c r="G65" s="3" t="n">
         <v>10.05</v>
@@ -5769,22 +5769,22 @@
         </is>
       </c>
       <c r="B66" s="3" t="n">
-        <v>73.16</v>
+        <v>73.12</v>
       </c>
       <c r="C66" s="3" t="n">
-        <v>64.65000000000001</v>
+        <v>64.76000000000001</v>
       </c>
       <c r="D66" s="3" t="n">
-        <v>61.6</v>
+        <v>61.74</v>
       </c>
       <c r="E66" s="3" t="n">
-        <v>57.81</v>
+        <v>57.85</v>
       </c>
       <c r="F66" s="3" t="n">
-        <v>44.69</v>
+        <v>44.83</v>
       </c>
       <c r="G66" s="3" t="n">
-        <v>21.67</v>
+        <v>21.7</v>
       </c>
       <c r="H66" s="3" t="n">
         <v>8.720000000000001</v>
@@ -5803,25 +5803,25 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>87.87</v>
+        <v>87.77</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>85.22</v>
+        <v>85.15000000000001</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>82.69</v>
+        <v>82.83</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>80.91</v>
+        <v>81.08</v>
       </c>
       <c r="F67" s="3" t="n">
         <v>63.84</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>39.45</v>
+        <v>39.52</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>23.62</v>
+        <v>23.66</v>
       </c>
       <c r="I67" s="3" t="n">
         <v>8.6</v>
@@ -5843,25 +5843,25 @@
         <v>58.33</v>
       </c>
       <c r="D68" s="3" t="n">
-        <v>54.65</v>
+        <v>54.69</v>
       </c>
       <c r="E68" s="3" t="n">
-        <v>46.7</v>
+        <v>46.74</v>
       </c>
       <c r="F68" s="3" t="n">
-        <v>29.1</v>
+        <v>29.13</v>
       </c>
       <c r="G68" s="3" t="n">
-        <v>22.05</v>
+        <v>22.08</v>
       </c>
       <c r="H68" s="3" t="n">
-        <v>16.49</v>
+        <v>16.53</v>
       </c>
       <c r="I68" s="3" t="n">
-        <v>5.94</v>
+        <v>6.01</v>
       </c>
       <c r="J68" s="3" t="n">
-        <v>5</v>
+        <v>5.07</v>
       </c>
     </row>
     <row r="69">
@@ -5871,25 +5871,25 @@
         </is>
       </c>
       <c r="B69" s="3" t="n">
-        <v>70.45999999999999</v>
+        <v>70.43000000000001</v>
       </c>
       <c r="C69" s="3" t="n">
         <v>68.72</v>
       </c>
       <c r="D69" s="3" t="n">
-        <v>64.45</v>
+        <v>64.38</v>
       </c>
       <c r="E69" s="3" t="n">
         <v>54.77</v>
       </c>
       <c r="F69" s="3" t="n">
-        <v>32.33</v>
+        <v>32.26</v>
       </c>
       <c r="G69" s="3" t="n">
-        <v>24.7</v>
+        <v>24.63</v>
       </c>
       <c r="H69" s="3" t="n">
-        <v>19.22</v>
+        <v>19.19</v>
       </c>
       <c r="I69" s="3" t="n">
         <v>6.72</v>
@@ -5905,25 +5905,25 @@
         </is>
       </c>
       <c r="B70" s="3" t="n">
-        <v>62.33</v>
+        <v>62.13</v>
       </c>
       <c r="C70" s="3" t="n">
-        <v>61.36</v>
+        <v>61.19</v>
       </c>
       <c r="D70" s="3" t="n">
-        <v>56.45</v>
+        <v>56.25</v>
       </c>
       <c r="E70" s="3" t="n">
-        <v>50.57</v>
+        <v>50.44</v>
       </c>
       <c r="F70" s="3" t="n">
-        <v>28.33</v>
+        <v>28.46</v>
       </c>
       <c r="G70" s="3" t="n">
-        <v>20.43</v>
+        <v>20.5</v>
       </c>
       <c r="H70" s="3" t="n">
-        <v>13.24</v>
+        <v>13.27</v>
       </c>
       <c r="I70" s="3" t="n">
         <v>4.81</v>
@@ -5939,22 +5939,22 @@
         </is>
       </c>
       <c r="B71" s="3" t="n">
-        <v>53.35</v>
+        <v>53.2</v>
       </c>
       <c r="C71" s="3" t="n">
-        <v>51.53</v>
+        <v>51.49</v>
       </c>
       <c r="D71" s="3" t="n">
-        <v>46.76</v>
+        <v>46.73</v>
       </c>
       <c r="E71" s="3" t="n">
         <v>36.24</v>
       </c>
       <c r="F71" s="3" t="n">
-        <v>15.89</v>
+        <v>15.92</v>
       </c>
       <c r="G71" s="3" t="n">
-        <v>8.67</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="H71" s="3" t="n">
         <v>4.72</v>
@@ -5973,25 +5973,25 @@
         </is>
       </c>
       <c r="B72" s="3" t="n">
-        <v>40.83</v>
+        <v>40.66</v>
       </c>
       <c r="C72" s="3" t="n">
-        <v>35.42</v>
+        <v>35.45</v>
       </c>
       <c r="D72" s="3" t="n">
-        <v>28.46</v>
+        <v>28.53</v>
       </c>
       <c r="E72" s="3" t="n">
-        <v>11.42</v>
+        <v>11.46</v>
       </c>
       <c r="F72" s="3" t="n">
-        <v>5.51</v>
+        <v>5.58</v>
       </c>
       <c r="G72" s="3" t="n">
-        <v>3.33</v>
+        <v>3.36</v>
       </c>
       <c r="H72" s="3" t="n">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="I72" s="3" t="n">
         <v>0.44</v>
@@ -6007,13 +6007,13 @@
         </is>
       </c>
       <c r="B73" s="3" t="n">
-        <v>40.83</v>
+        <v>40.62</v>
       </c>
       <c r="C73" s="3" t="n">
-        <v>36.08</v>
+        <v>36.11</v>
       </c>
       <c r="D73" s="3" t="n">
-        <v>30.45</v>
+        <v>30.52</v>
       </c>
       <c r="E73" s="3" t="n">
         <v>8.92</v>
@@ -6041,13 +6041,13 @@
         </is>
       </c>
       <c r="B74" s="3" t="n">
-        <v>30.51</v>
+        <v>30.41</v>
       </c>
       <c r="C74" s="3" t="n">
-        <v>28.56</v>
+        <v>28.76</v>
       </c>
       <c r="D74" s="3" t="n">
-        <v>18.68</v>
+        <v>18.62</v>
       </c>
       <c r="E74" s="3" t="n">
         <v>5.51</v>
@@ -6075,7 +6075,7 @@
         </is>
       </c>
       <c r="B75" s="3" t="n">
-        <v>6.39</v>
+        <v>6.28</v>
       </c>
       <c r="C75" s="3" t="n">
         <v>5.24</v>
@@ -6143,10 +6143,10 @@
         </is>
       </c>
       <c r="B77" s="3" t="n">
-        <v>24.06</v>
+        <v>23.92</v>
       </c>
       <c r="C77" s="3" t="n">
-        <v>14.72</v>
+        <v>14.75</v>
       </c>
       <c r="D77" s="3" t="n">
         <v>0.67</v>
@@ -6177,16 +6177,16 @@
         </is>
       </c>
       <c r="B78" s="3" t="n">
-        <v>66.67</v>
+        <v>66.73999999999999</v>
       </c>
       <c r="C78" s="3" t="n">
-        <v>45.83</v>
+        <v>46.01</v>
       </c>
       <c r="D78" s="3" t="n">
-        <v>17.88</v>
+        <v>17.95</v>
       </c>
       <c r="E78" s="3" t="n">
-        <v>8.44</v>
+        <v>8.51</v>
       </c>
       <c r="F78" s="3" t="n">
         <v>6.7</v>
@@ -6211,25 +6211,25 @@
         </is>
       </c>
       <c r="B79" s="3" t="n">
-        <v>70.40000000000001</v>
+        <v>70.36</v>
       </c>
       <c r="C79" s="3" t="n">
-        <v>57.66</v>
+        <v>57.83</v>
       </c>
       <c r="D79" s="3" t="n">
-        <v>27.08</v>
+        <v>27.15</v>
       </c>
       <c r="E79" s="3" t="n">
-        <v>15.32</v>
+        <v>15.36</v>
       </c>
       <c r="F79" s="3" t="n">
-        <v>8.74</v>
+        <v>8.77</v>
       </c>
       <c r="G79" s="3" t="n">
-        <v>7.39</v>
+        <v>7.43</v>
       </c>
       <c r="H79" s="3" t="n">
-        <v>1.88</v>
+        <v>1.92</v>
       </c>
       <c r="I79" s="3" t="n">
         <v>0.3</v>
@@ -6245,13 +6245,13 @@
         </is>
       </c>
       <c r="B80" s="3" t="n">
-        <v>88.3</v>
+        <v>88.06</v>
       </c>
       <c r="C80" s="3" t="n">
-        <v>70.09999999999999</v>
+        <v>70.20999999999999</v>
       </c>
       <c r="D80" s="3" t="n">
-        <v>28.85</v>
+        <v>28.92</v>
       </c>
       <c r="E80" s="3" t="n">
         <v>16.81</v>
@@ -6279,31 +6279,31 @@
         </is>
       </c>
       <c r="B81" s="3" t="n">
-        <v>71.27</v>
+        <v>70.97</v>
       </c>
       <c r="C81" s="3" t="n">
         <v>50.67</v>
       </c>
       <c r="D81" s="3" t="n">
-        <v>34.78</v>
+        <v>34.81</v>
       </c>
       <c r="E81" s="3" t="n">
-        <v>28.7</v>
+        <v>28.8</v>
       </c>
       <c r="F81" s="3" t="n">
-        <v>25.24</v>
+        <v>25.37</v>
       </c>
       <c r="G81" s="3" t="n">
-        <v>23.79</v>
+        <v>23.92</v>
       </c>
       <c r="H81" s="3" t="n">
-        <v>13.41</v>
+        <v>13.51</v>
       </c>
       <c r="I81" s="3" t="n">
-        <v>7.93</v>
+        <v>7.96</v>
       </c>
       <c r="J81" s="3" t="n">
-        <v>7.46</v>
+        <v>7.49</v>
       </c>
     </row>
     <row r="82">
@@ -6313,25 +6313,25 @@
         </is>
       </c>
       <c r="B82" s="3" t="n">
-        <v>53.97</v>
+        <v>53.8</v>
       </c>
       <c r="C82" s="3" t="n">
-        <v>28.53</v>
+        <v>28.43</v>
       </c>
       <c r="D82" s="3" t="n">
-        <v>16.4</v>
+        <v>16.47</v>
       </c>
       <c r="E82" s="3" t="n">
-        <v>12.03</v>
+        <v>12.1</v>
       </c>
       <c r="F82" s="3" t="n">
-        <v>9.91</v>
+        <v>9.98</v>
       </c>
       <c r="G82" s="3" t="n">
-        <v>8.300000000000001</v>
+        <v>8.33</v>
       </c>
       <c r="H82" s="3" t="n">
-        <v>6.15</v>
+        <v>6.22</v>
       </c>
       <c r="I82" s="3" t="n">
         <v>2.99</v>
@@ -6347,16 +6347,16 @@
         </is>
       </c>
       <c r="B83" s="3" t="n">
-        <v>48.14</v>
+        <v>48.1</v>
       </c>
       <c r="C83" s="3" t="n">
-        <v>15.1</v>
+        <v>15.14</v>
       </c>
       <c r="D83" s="3" t="n">
-        <v>7.92</v>
+        <v>7.96</v>
       </c>
       <c r="E83" s="3" t="n">
-        <v>4.17</v>
+        <v>4.2</v>
       </c>
       <c r="F83" s="3" t="n">
         <v>2.01</v>
@@ -6381,25 +6381,25 @@
         </is>
       </c>
       <c r="B84" s="3" t="n">
-        <v>54.13</v>
+        <v>54.2</v>
       </c>
       <c r="C84" s="3" t="n">
-        <v>25.1</v>
+        <v>25.2</v>
       </c>
       <c r="D84" s="3" t="n">
-        <v>12.77</v>
+        <v>12.84</v>
       </c>
       <c r="E84" s="3" t="n">
-        <v>10.35</v>
+        <v>10.42</v>
       </c>
       <c r="F84" s="3" t="n">
-        <v>4.94</v>
+        <v>4.97</v>
       </c>
       <c r="G84" s="3" t="n">
-        <v>3.46</v>
+        <v>3.49</v>
       </c>
       <c r="H84" s="3" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="I84" s="3" t="n">
         <v>0.03</v>
@@ -6415,19 +6415,19 @@
         </is>
       </c>
       <c r="B85" s="3" t="n">
-        <v>56.49</v>
+        <v>56.35</v>
       </c>
       <c r="C85" s="3" t="n">
-        <v>21.25</v>
+        <v>21.35</v>
       </c>
       <c r="D85" s="3" t="n">
-        <v>10.24</v>
+        <v>10.31</v>
       </c>
       <c r="E85" s="3" t="n">
-        <v>7.81</v>
+        <v>7.85</v>
       </c>
       <c r="F85" s="3" t="n">
-        <v>5.97</v>
+        <v>6.01</v>
       </c>
       <c r="G85" s="3" t="n">
         <v>4.62</v>
@@ -6449,10 +6449,10 @@
         </is>
       </c>
       <c r="B86" s="3" t="n">
-        <v>21.64</v>
+        <v>21.4</v>
       </c>
       <c r="C86" s="3" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="D86" s="3" t="n">
         <v>0.03</v>
@@ -6517,7 +6517,7 @@
         </is>
       </c>
       <c r="B88" s="3" t="n">
-        <v>14.35</v>
+        <v>14.11</v>
       </c>
       <c r="C88" s="3" t="n">
         <v>1.24</v>
@@ -6551,7 +6551,7 @@
         </is>
       </c>
       <c r="B89" s="3" t="n">
-        <v>22.55</v>
+        <v>22.51</v>
       </c>
       <c r="C89" s="3" t="n">
         <v>3.26</v>
@@ -6780,7 +6780,7 @@
         <v>2976</v>
       </c>
       <c r="C2" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D2" s="6" t="n">
         <v>1</v>
@@ -6817,7 +6817,7 @@
         <v>2880</v>
       </c>
       <c r="C3" s="6" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D3" s="6" t="n">
         <v>3</v>
@@ -6854,7 +6854,7 @@
         <v>2976</v>
       </c>
       <c r="C4" s="6" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D4" s="6" t="n">
         <v>21</v>
@@ -6891,7 +6891,7 @@
         <v>2976</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="D5" s="6" t="n">
         <v>40</v>
@@ -6928,7 +6928,7 @@
         <v>2880</v>
       </c>
       <c r="C6" s="6" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D6" s="6" t="n">
         <v>8</v>
@@ -6965,7 +6965,7 @@
         <v>2976</v>
       </c>
       <c r="C7" s="6" t="n">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="D7" s="6" t="n">
         <v>60</v>
@@ -7039,31 +7039,31 @@
         <v>2976</v>
       </c>
       <c r="C9" s="6" t="n">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J9" s="6" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K9" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
@@ -7076,16 +7076,16 @@
         <v>2976</v>
       </c>
       <c r="C10" s="6" t="n">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E10" s="6" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="G10" s="6" t="n">
         <v>72</v>
@@ -7113,7 +7113,7 @@
         <v>2784</v>
       </c>
       <c r="C11" s="6" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D11" s="6" t="n">
         <v>15</v>
@@ -7150,7 +7150,7 @@
         <v>2976</v>
       </c>
       <c r="C12" s="6" t="n">
-        <v>70</v>
+        <v>20</v>
       </c>
       <c r="D12" s="6" t="n">
         <v>7</v>
@@ -7187,7 +7187,7 @@
         <v>2880</v>
       </c>
       <c r="C13" s="6" t="n">
-        <v>168</v>
+        <v>138</v>
       </c>
       <c r="D13" s="6" t="n">
         <v>75</v>
@@ -7224,7 +7224,7 @@
         <v>2976</v>
       </c>
       <c r="C14" s="6" t="n">
-        <v>95</v>
+        <v>72</v>
       </c>
       <c r="D14" s="6" t="n">
         <v>30</v>
@@ -7261,7 +7261,7 @@
         <v>2880</v>
       </c>
       <c r="C15" s="6" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D15" s="6" t="n">
         <v>5</v>
@@ -7298,7 +7298,7 @@
         <v>2976</v>
       </c>
       <c r="C16" s="6" t="n">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="D16" s="6" t="n">
         <v>7</v>
@@ -7335,16 +7335,16 @@
         <v>2976</v>
       </c>
       <c r="C17" s="6" t="n">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D17" s="6" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E17" s="6" t="n">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G17" s="6" t="n">
         <v>25</v>
@@ -7372,7 +7372,7 @@
         <v>2880</v>
       </c>
       <c r="C18" s="6" t="n">
-        <v>295</v>
+        <v>285</v>
       </c>
       <c r="D18" s="6" t="n">
         <v>225</v>
@@ -7381,7 +7381,7 @@
         <v>206</v>
       </c>
       <c r="F18" s="6" t="n">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="G18" s="6" t="n">
         <v>97</v>
@@ -7409,19 +7409,19 @@
         <v>2976</v>
       </c>
       <c r="C19" s="6" t="n">
-        <v>302</v>
+        <v>288</v>
       </c>
       <c r="D19" s="6" t="n">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="E19" s="6" t="n">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="H19" s="6" t="n">
         <v>11</v>
@@ -7446,19 +7446,19 @@
         <v>2880</v>
       </c>
       <c r="C20" s="6" t="n">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="D20" s="6" t="n">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E20" s="6" t="n">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F20" s="6" t="n">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H20" s="6" t="n">
         <v>8</v>
@@ -7483,10 +7483,10 @@
         <v>2976</v>
       </c>
       <c r="C21" s="6" t="n">
-        <v>718</v>
+        <v>687</v>
       </c>
       <c r="D21" s="6" t="n">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E21" s="6" t="n">
         <v>465</v>
@@ -7520,16 +7520,16 @@
         <v>2976</v>
       </c>
       <c r="C22" s="6" t="n">
-        <v>788</v>
+        <v>776</v>
       </c>
       <c r="D22" s="6" t="n">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="E22" s="6" t="n">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="F22" s="6" t="n">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="G22" s="6" t="n">
         <v>178</v>
@@ -7557,16 +7557,16 @@
         <v>2688</v>
       </c>
       <c r="C23" s="6" t="n">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="D23" s="6" t="n">
         <v>435</v>
       </c>
       <c r="E23" s="6" t="n">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="G23" s="6" t="n">
         <v>150</v>
@@ -7594,16 +7594,16 @@
         <v>2976</v>
       </c>
       <c r="C24" s="6" t="n">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="D24" s="6" t="n">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="E24" s="6" t="n">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="F24" s="6" t="n">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="G24" s="6" t="n">
         <v>19</v>
@@ -7631,7 +7631,7 @@
         <v>2880</v>
       </c>
       <c r="C25" s="6" t="n">
-        <v>463</v>
+        <v>453</v>
       </c>
       <c r="D25" s="6" t="n">
         <v>330</v>
@@ -7643,7 +7643,7 @@
         <v>224</v>
       </c>
       <c r="G25" s="6" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H25" s="6" t="n">
         <v>22</v>
@@ -7668,7 +7668,7 @@
         <v>2976</v>
       </c>
       <c r="C26" s="6" t="n">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D26" s="6" t="n">
         <v>189</v>
@@ -7742,7 +7742,7 @@
         <v>2976</v>
       </c>
       <c r="C28" s="6" t="n">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="D28" s="6" t="n">
         <v>363</v>
@@ -7779,10 +7779,10 @@
         <v>2976</v>
       </c>
       <c r="C29" s="6" t="n">
-        <v>1012</v>
+        <v>1015</v>
       </c>
       <c r="D29" s="6" t="n">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="E29" s="6" t="n">
         <v>749</v>
@@ -7816,22 +7816,22 @@
         <v>2880</v>
       </c>
       <c r="C30" s="6" t="n">
-        <v>1574</v>
+        <v>1567</v>
       </c>
       <c r="D30" s="6" t="n">
-        <v>1333</v>
+        <v>1327</v>
       </c>
       <c r="E30" s="6" t="n">
-        <v>1061</v>
+        <v>1055</v>
       </c>
       <c r="F30" s="6" t="n">
-        <v>805</v>
+        <v>803</v>
       </c>
       <c r="G30" s="6" t="n">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="H30" s="6" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="I30" s="6" t="n">
         <v>25</v>
@@ -7853,7 +7853,7 @@
         <v>2976</v>
       </c>
       <c r="C31" s="6" t="n">
-        <v>2066</v>
+        <v>2071</v>
       </c>
       <c r="D31" s="6" t="n">
         <v>1763</v>
@@ -7862,7 +7862,7 @@
         <v>1508</v>
       </c>
       <c r="F31" s="6" t="n">
-        <v>1150</v>
+        <v>1152</v>
       </c>
       <c r="G31" s="6" t="n">
         <v>452</v>
@@ -7890,31 +7890,31 @@
         <v>2880</v>
       </c>
       <c r="C32" s="6" t="n">
-        <v>885</v>
+        <v>878</v>
       </c>
       <c r="D32" s="6" t="n">
         <v>757</v>
       </c>
       <c r="E32" s="6" t="n">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="F32" s="6" t="n">
         <v>567</v>
       </c>
       <c r="G32" s="6" t="n">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="H32" s="6" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="I32" s="6" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J32" s="6" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="K32" s="6" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="33">
@@ -7927,22 +7927,22 @@
         <v>2976</v>
       </c>
       <c r="C33" s="6" t="n">
-        <v>1309</v>
+        <v>1303</v>
       </c>
       <c r="D33" s="6" t="n">
-        <v>1075</v>
+        <v>1069</v>
       </c>
       <c r="E33" s="6" t="n">
-        <v>908</v>
+        <v>906</v>
       </c>
       <c r="F33" s="6" t="n">
         <v>733</v>
       </c>
       <c r="G33" s="6" t="n">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H33" s="6" t="n">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="I33" s="6" t="n">
         <v>7</v>
@@ -7964,19 +7964,19 @@
         <v>2976</v>
       </c>
       <c r="C34" s="6" t="n">
-        <v>658</v>
+        <v>654</v>
       </c>
       <c r="D34" s="6" t="n">
-        <v>532</v>
+        <v>526</v>
       </c>
       <c r="E34" s="6" t="n">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="F34" s="6" t="n">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="G34" s="6" t="n">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="H34" s="6" t="n">
         <v>40</v>
@@ -8001,19 +8001,19 @@
         <v>2688</v>
       </c>
       <c r="C35" s="6" t="n">
-        <v>806</v>
+        <v>802</v>
       </c>
       <c r="D35" s="6" t="n">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="E35" s="6" t="n">
-        <v>532</v>
+        <v>526</v>
       </c>
       <c r="F35" s="6" t="n">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="G35" s="6" t="n">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="H35" s="6" t="n">
         <v>27</v>
@@ -8038,19 +8038,19 @@
         <v>2976</v>
       </c>
       <c r="C36" s="6" t="n">
-        <v>1018</v>
+        <v>1013</v>
       </c>
       <c r="D36" s="6" t="n">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="E36" s="6" t="n">
         <v>618</v>
       </c>
       <c r="F36" s="6" t="n">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="G36" s="6" t="n">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="H36" s="6" t="n">
         <v>86</v>
@@ -8075,16 +8075,16 @@
         <v>2880</v>
       </c>
       <c r="C37" s="6" t="n">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="D37" s="6" t="n">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="E37" s="6" t="n">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="F37" s="6" t="n">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="G37" s="6" t="n">
         <v>210</v>
@@ -8112,10 +8112,10 @@
         <v>2976</v>
       </c>
       <c r="C38" s="6" t="n">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D38" s="6" t="n">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E38" s="6" t="n">
         <v>156</v>
@@ -8186,7 +8186,7 @@
         <v>2976</v>
       </c>
       <c r="C40" s="6" t="n">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D40" s="6" t="n">
         <v>329</v>
@@ -8223,16 +8223,16 @@
         <v>2976</v>
       </c>
       <c r="C41" s="6" t="n">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="D41" s="6" t="n">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="E41" s="6" t="n">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="F41" s="6" t="n">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="G41" s="6" t="n">
         <v>217</v>
@@ -8260,16 +8260,16 @@
         <v>2880</v>
       </c>
       <c r="C42" s="6" t="n">
-        <v>889</v>
+        <v>882</v>
       </c>
       <c r="D42" s="6" t="n">
-        <v>837</v>
+        <v>835</v>
       </c>
       <c r="E42" s="6" t="n">
-        <v>733</v>
+        <v>731</v>
       </c>
       <c r="F42" s="6" t="n">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="G42" s="6" t="n">
         <v>336</v>
@@ -8297,16 +8297,16 @@
         <v>2976</v>
       </c>
       <c r="C43" s="6" t="n">
-        <v>1182</v>
+        <v>1183</v>
       </c>
       <c r="D43" s="6" t="n">
-        <v>1102</v>
+        <v>1103</v>
       </c>
       <c r="E43" s="6" t="n">
         <v>994</v>
       </c>
       <c r="F43" s="6" t="n">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="G43" s="6" t="n">
         <v>495</v>
@@ -8334,31 +8334,31 @@
         <v>2880</v>
       </c>
       <c r="C44" s="6" t="n">
-        <v>1578</v>
+        <v>1575</v>
       </c>
       <c r="D44" s="6" t="n">
-        <v>1458</v>
+        <v>1455</v>
       </c>
       <c r="E44" s="6" t="n">
-        <v>1297</v>
+        <v>1296</v>
       </c>
       <c r="F44" s="6" t="n">
         <v>1239</v>
       </c>
       <c r="G44" s="6" t="n">
-        <v>710</v>
+        <v>707</v>
       </c>
       <c r="H44" s="6" t="n">
-        <v>580</v>
+        <v>576</v>
       </c>
       <c r="I44" s="6" t="n">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="J44" s="6" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="K44" s="6" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="45">
@@ -8371,31 +8371,31 @@
         <v>2976</v>
       </c>
       <c r="C45" s="6" t="n">
-        <v>2305</v>
+        <v>2294</v>
       </c>
       <c r="D45" s="6" t="n">
-        <v>2176</v>
+        <v>2165</v>
       </c>
       <c r="E45" s="6" t="n">
-        <v>1999</v>
+        <v>1990</v>
       </c>
       <c r="F45" s="6" t="n">
-        <v>1881</v>
+        <v>1877</v>
       </c>
       <c r="G45" s="6" t="n">
-        <v>1419</v>
+        <v>1420</v>
       </c>
       <c r="H45" s="6" t="n">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="I45" s="6" t="n">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="J45" s="6" t="n">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="K45" s="6" t="n">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="46">
@@ -8408,25 +8408,25 @@
         <v>2976</v>
       </c>
       <c r="C46" s="6" t="n">
-        <v>1668</v>
+        <v>1666</v>
       </c>
       <c r="D46" s="6" t="n">
-        <v>1581</v>
+        <v>1580</v>
       </c>
       <c r="E46" s="6" t="n">
-        <v>1495</v>
+        <v>1493</v>
       </c>
       <c r="F46" s="6" t="n">
-        <v>1413</v>
+        <v>1411</v>
       </c>
       <c r="G46" s="6" t="n">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="H46" s="6" t="n">
-        <v>861</v>
+        <v>858</v>
       </c>
       <c r="I46" s="6" t="n">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="J46" s="6" t="n">
         <v>160</v>
@@ -8445,25 +8445,25 @@
         <v>2688</v>
       </c>
       <c r="C47" s="6" t="n">
-        <v>1648</v>
+        <v>1647</v>
       </c>
       <c r="D47" s="6" t="n">
-        <v>1560</v>
+        <v>1559</v>
       </c>
       <c r="E47" s="6" t="n">
-        <v>1449</v>
+        <v>1448</v>
       </c>
       <c r="F47" s="6" t="n">
         <v>1413</v>
       </c>
       <c r="G47" s="6" t="n">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="H47" s="6" t="n">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="I47" s="6" t="n">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="J47" s="6" t="n">
         <v>90</v>
@@ -8482,22 +8482,22 @@
         <v>2976</v>
       </c>
       <c r="C48" s="6" t="n">
-        <v>1560</v>
+        <v>1559</v>
       </c>
       <c r="D48" s="6" t="n">
-        <v>1426</v>
+        <v>1429</v>
       </c>
       <c r="E48" s="6" t="n">
-        <v>1245</v>
+        <v>1249</v>
       </c>
       <c r="F48" s="6" t="n">
-        <v>1181</v>
+        <v>1184</v>
       </c>
       <c r="G48" s="6" t="n">
-        <v>932</v>
+        <v>936</v>
       </c>
       <c r="H48" s="6" t="n">
-        <v>603</v>
+        <v>606</v>
       </c>
       <c r="I48" s="6" t="n">
         <v>43</v>
@@ -8519,19 +8519,19 @@
         <v>2880</v>
       </c>
       <c r="C49" s="6" t="n">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="D49" s="6" t="n">
-        <v>778</v>
+        <v>780</v>
       </c>
       <c r="E49" s="6" t="n">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="F49" s="6" t="n">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="G49" s="6" t="n">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H49" s="6" t="n">
         <v>189</v>
@@ -8556,7 +8556,7 @@
         <v>2976</v>
       </c>
       <c r="C50" s="6" t="n">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="D50" s="6" t="n">
         <v>191</v>
@@ -8593,10 +8593,10 @@
         <v>2880</v>
       </c>
       <c r="C51" s="6" t="n">
-        <v>671</v>
+        <v>668</v>
       </c>
       <c r="D51" s="6" t="n">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="E51" s="6" t="n">
         <v>474</v>
@@ -8630,19 +8630,19 @@
         <v>2976</v>
       </c>
       <c r="C52" s="6" t="n">
-        <v>975</v>
+        <v>962</v>
       </c>
       <c r="D52" s="6" t="n">
         <v>832</v>
       </c>
       <c r="E52" s="6" t="n">
-        <v>673</v>
+        <v>663</v>
       </c>
       <c r="F52" s="6" t="n">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="G52" s="6" t="n">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="H52" s="6" t="n">
         <v>347</v>
@@ -8667,22 +8667,22 @@
         <v>2976</v>
       </c>
       <c r="C53" s="6" t="n">
-        <v>1009</v>
+        <v>1003</v>
       </c>
       <c r="D53" s="6" t="n">
-        <v>837</v>
+        <v>839</v>
       </c>
       <c r="E53" s="6" t="n">
-        <v>684</v>
+        <v>678</v>
       </c>
       <c r="F53" s="6" t="n">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="G53" s="6" t="n">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="H53" s="6" t="n">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="I53" s="6" t="n">
         <v>3</v>
@@ -8704,13 +8704,13 @@
         <v>2880</v>
       </c>
       <c r="C54" s="6" t="n">
-        <v>1932</v>
+        <v>1935</v>
       </c>
       <c r="D54" s="6" t="n">
-        <v>1810</v>
+        <v>1811</v>
       </c>
       <c r="E54" s="6" t="n">
-        <v>1743</v>
+        <v>1742</v>
       </c>
       <c r="F54" s="6" t="n">
         <v>1701</v>
@@ -8719,7 +8719,7 @@
         <v>1670</v>
       </c>
       <c r="H54" s="6" t="n">
-        <v>1493</v>
+        <v>1495</v>
       </c>
       <c r="I54" s="6" t="n">
         <v>379</v>
@@ -8744,7 +8744,7 @@
         <v>1925</v>
       </c>
       <c r="D55" s="6" t="n">
-        <v>1798</v>
+        <v>1802</v>
       </c>
       <c r="E55" s="6" t="n">
         <v>1579</v>
@@ -8756,16 +8756,16 @@
         <v>1445</v>
       </c>
       <c r="H55" s="6" t="n">
-        <v>1106</v>
+        <v>1111</v>
       </c>
       <c r="I55" s="6" t="n">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="J55" s="6" t="n">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="K55" s="6" t="n">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="56">
@@ -8778,22 +8778,22 @@
         <v>2880</v>
       </c>
       <c r="C56" s="6" t="n">
-        <v>1819</v>
+        <v>1820</v>
       </c>
       <c r="D56" s="6" t="n">
         <v>1731</v>
       </c>
       <c r="E56" s="6" t="n">
-        <v>1573</v>
+        <v>1574</v>
       </c>
       <c r="F56" s="6" t="n">
-        <v>1503</v>
+        <v>1504</v>
       </c>
       <c r="G56" s="6" t="n">
-        <v>1394</v>
+        <v>1395</v>
       </c>
       <c r="H56" s="6" t="n">
-        <v>1085</v>
+        <v>1086</v>
       </c>
       <c r="I56" s="6" t="n">
         <v>317</v>
@@ -8815,31 +8815,31 @@
         <v>2976</v>
       </c>
       <c r="C57" s="6" t="n">
-        <v>1938</v>
+        <v>1940</v>
       </c>
       <c r="D57" s="6" t="n">
-        <v>1886</v>
+        <v>1887</v>
       </c>
       <c r="E57" s="6" t="n">
-        <v>1798</v>
+        <v>1800</v>
       </c>
       <c r="F57" s="6" t="n">
-        <v>1741</v>
+        <v>1746</v>
       </c>
       <c r="G57" s="6" t="n">
-        <v>1589</v>
+        <v>1593</v>
       </c>
       <c r="H57" s="6" t="n">
-        <v>1371</v>
+        <v>1373</v>
       </c>
       <c r="I57" s="6" t="n">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="J57" s="6" t="n">
         <v>365</v>
       </c>
       <c r="K57" s="6" t="n">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="58">
@@ -8858,25 +8858,25 @@
         <v>1715</v>
       </c>
       <c r="E58" s="6" t="n">
-        <v>1443</v>
+        <v>1444</v>
       </c>
       <c r="F58" s="6" t="n">
-        <v>1267</v>
+        <v>1269</v>
       </c>
       <c r="G58" s="6" t="n">
-        <v>1149</v>
+        <v>1152</v>
       </c>
       <c r="H58" s="6" t="n">
-        <v>963</v>
+        <v>967</v>
       </c>
       <c r="I58" s="6" t="n">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="J58" s="6" t="n">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="K58" s="6" t="n">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="59">
@@ -8889,25 +8889,25 @@
         <v>2784</v>
       </c>
       <c r="C59" s="6" t="n">
-        <v>1724</v>
+        <v>1723</v>
       </c>
       <c r="D59" s="6" t="n">
-        <v>1703</v>
+        <v>1704</v>
       </c>
       <c r="E59" s="6" t="n">
-        <v>1545</v>
+        <v>1546</v>
       </c>
       <c r="F59" s="6" t="n">
-        <v>1450</v>
+        <v>1452</v>
       </c>
       <c r="G59" s="6" t="n">
-        <v>1405</v>
+        <v>1408</v>
       </c>
       <c r="H59" s="6" t="n">
-        <v>1069</v>
+        <v>1072</v>
       </c>
       <c r="I59" s="6" t="n">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="J59" s="6" t="n">
         <v>212</v>
@@ -8926,22 +8926,22 @@
         <v>2976</v>
       </c>
       <c r="C60" s="6" t="n">
-        <v>1370</v>
+        <v>1367</v>
       </c>
       <c r="D60" s="6" t="n">
-        <v>1321</v>
+        <v>1318</v>
       </c>
       <c r="E60" s="6" t="n">
-        <v>1168</v>
+        <v>1165</v>
       </c>
       <c r="F60" s="6" t="n">
-        <v>1050</v>
+        <v>1049</v>
       </c>
       <c r="G60" s="6" t="n">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="H60" s="6" t="n">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="I60" s="6" t="n">
         <v>221</v>
@@ -8963,7 +8963,7 @@
         <v>2880</v>
       </c>
       <c r="C61" s="6" t="n">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="D61" s="6" t="n">
         <v>756</v>
@@ -9000,10 +9000,10 @@
         <v>2976</v>
       </c>
       <c r="C62" s="6" t="n">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="D62" s="6" t="n">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="E62" s="6" t="n">
         <v>290</v>
@@ -9111,19 +9111,19 @@
         <v>2976</v>
       </c>
       <c r="C65" s="6" t="n">
-        <v>1244</v>
+        <v>1246</v>
       </c>
       <c r="D65" s="6" t="n">
-        <v>1154</v>
+        <v>1155</v>
       </c>
       <c r="E65" s="6" t="n">
-        <v>1050</v>
+        <v>1052</v>
       </c>
       <c r="F65" s="6" t="n">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="G65" s="6" t="n">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="H65" s="6" t="n">
         <v>299</v>
@@ -9148,22 +9148,22 @@
         <v>2880</v>
       </c>
       <c r="C66" s="6" t="n">
-        <v>2107</v>
+        <v>2106</v>
       </c>
       <c r="D66" s="6" t="n">
-        <v>1862</v>
+        <v>1865</v>
       </c>
       <c r="E66" s="6" t="n">
-        <v>1774</v>
+        <v>1778</v>
       </c>
       <c r="F66" s="6" t="n">
-        <v>1665</v>
+        <v>1666</v>
       </c>
       <c r="G66" s="6" t="n">
-        <v>1287</v>
+        <v>1291</v>
       </c>
       <c r="H66" s="6" t="n">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="I66" s="6" t="n">
         <v>251</v>
@@ -9185,25 +9185,25 @@
         <v>2976</v>
       </c>
       <c r="C67" s="6" t="n">
-        <v>2615</v>
+        <v>2612</v>
       </c>
       <c r="D67" s="6" t="n">
-        <v>2536</v>
+        <v>2534</v>
       </c>
       <c r="E67" s="6" t="n">
-        <v>2461</v>
+        <v>2465</v>
       </c>
       <c r="F67" s="6" t="n">
-        <v>2408</v>
+        <v>2413</v>
       </c>
       <c r="G67" s="6" t="n">
         <v>1900</v>
       </c>
       <c r="H67" s="6" t="n">
-        <v>1174</v>
+        <v>1176</v>
       </c>
       <c r="I67" s="6" t="n">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="J67" s="6" t="n">
         <v>256</v>
@@ -9228,25 +9228,25 @@
         <v>1680</v>
       </c>
       <c r="E68" s="6" t="n">
-        <v>1574</v>
+        <v>1575</v>
       </c>
       <c r="F68" s="6" t="n">
-        <v>1345</v>
+        <v>1346</v>
       </c>
       <c r="G68" s="6" t="n">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="H68" s="6" t="n">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="I68" s="6" t="n">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="J68" s="6" t="n">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="K68" s="6" t="n">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="69">
@@ -9259,25 +9259,25 @@
         <v>2976</v>
       </c>
       <c r="C69" s="6" t="n">
-        <v>2097</v>
+        <v>2096</v>
       </c>
       <c r="D69" s="6" t="n">
         <v>2045</v>
       </c>
       <c r="E69" s="6" t="n">
-        <v>1918</v>
+        <v>1916</v>
       </c>
       <c r="F69" s="6" t="n">
         <v>1630</v>
       </c>
       <c r="G69" s="6" t="n">
-        <v>962</v>
+        <v>960</v>
       </c>
       <c r="H69" s="6" t="n">
-        <v>735</v>
+        <v>733</v>
       </c>
       <c r="I69" s="6" t="n">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="J69" s="6" t="n">
         <v>200</v>
@@ -9296,25 +9296,25 @@
         <v>2976</v>
       </c>
       <c r="C70" s="6" t="n">
-        <v>1855</v>
+        <v>1849</v>
       </c>
       <c r="D70" s="6" t="n">
-        <v>1826</v>
+        <v>1821</v>
       </c>
       <c r="E70" s="6" t="n">
-        <v>1680</v>
+        <v>1674</v>
       </c>
       <c r="F70" s="6" t="n">
-        <v>1505</v>
+        <v>1501</v>
       </c>
       <c r="G70" s="6" t="n">
-        <v>843</v>
+        <v>847</v>
       </c>
       <c r="H70" s="6" t="n">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="I70" s="6" t="n">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="J70" s="6" t="n">
         <v>143</v>
@@ -9333,22 +9333,22 @@
         <v>2688</v>
       </c>
       <c r="C71" s="6" t="n">
-        <v>1434</v>
+        <v>1430</v>
       </c>
       <c r="D71" s="6" t="n">
-        <v>1385</v>
+        <v>1384</v>
       </c>
       <c r="E71" s="6" t="n">
-        <v>1257</v>
+        <v>1256</v>
       </c>
       <c r="F71" s="6" t="n">
         <v>974</v>
       </c>
       <c r="G71" s="6" t="n">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="H71" s="6" t="n">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="I71" s="6" t="n">
         <v>127</v>
@@ -9370,25 +9370,25 @@
         <v>2976</v>
       </c>
       <c r="C72" s="6" t="n">
-        <v>1215</v>
+        <v>1210</v>
       </c>
       <c r="D72" s="6" t="n">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="E72" s="6" t="n">
-        <v>847</v>
+        <v>849</v>
       </c>
       <c r="F72" s="6" t="n">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="G72" s="6" t="n">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="H72" s="6" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="I72" s="6" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="J72" s="6" t="n">
         <v>13</v>
@@ -9407,13 +9407,13 @@
         <v>2880</v>
       </c>
       <c r="C73" s="6" t="n">
-        <v>1176</v>
+        <v>1170</v>
       </c>
       <c r="D73" s="6" t="n">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="E73" s="6" t="n">
-        <v>877</v>
+        <v>879</v>
       </c>
       <c r="F73" s="6" t="n">
         <v>257</v>
@@ -9444,13 +9444,13 @@
         <v>2976</v>
       </c>
       <c r="C74" s="6" t="n">
-        <v>908</v>
+        <v>905</v>
       </c>
       <c r="D74" s="6" t="n">
-        <v>850</v>
+        <v>856</v>
       </c>
       <c r="E74" s="6" t="n">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="F74" s="6" t="n">
         <v>164</v>
@@ -9481,7 +9481,7 @@
         <v>2880</v>
       </c>
       <c r="C75" s="6" t="n">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="D75" s="6" t="n">
         <v>151</v>
@@ -9555,10 +9555,10 @@
         <v>2976</v>
       </c>
       <c r="C77" s="6" t="n">
-        <v>716</v>
+        <v>712</v>
       </c>
       <c r="D77" s="6" t="n">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="E77" s="6" t="n">
         <v>20</v>
@@ -9592,16 +9592,16 @@
         <v>2880</v>
       </c>
       <c r="C78" s="6" t="n">
-        <v>1920</v>
+        <v>1922</v>
       </c>
       <c r="D78" s="6" t="n">
-        <v>1320</v>
+        <v>1325</v>
       </c>
       <c r="E78" s="6" t="n">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="F78" s="6" t="n">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="G78" s="6" t="n">
         <v>193</v>
@@ -9629,25 +9629,25 @@
         <v>2976</v>
       </c>
       <c r="C79" s="6" t="n">
-        <v>2095</v>
+        <v>2094</v>
       </c>
       <c r="D79" s="6" t="n">
-        <v>1716</v>
+        <v>1721</v>
       </c>
       <c r="E79" s="6" t="n">
-        <v>806</v>
+        <v>808</v>
       </c>
       <c r="F79" s="6" t="n">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="G79" s="6" t="n">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H79" s="6" t="n">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="I79" s="6" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="J79" s="6" t="n">
         <v>9</v>
@@ -9666,13 +9666,13 @@
         <v>2880</v>
       </c>
       <c r="C80" s="6" t="n">
-        <v>2543</v>
+        <v>2536</v>
       </c>
       <c r="D80" s="6" t="n">
-        <v>2019</v>
+        <v>2022</v>
       </c>
       <c r="E80" s="6" t="n">
-        <v>831</v>
+        <v>833</v>
       </c>
       <c r="F80" s="6" t="n">
         <v>484</v>
@@ -9703,31 +9703,31 @@
         <v>2976</v>
       </c>
       <c r="C81" s="6" t="n">
-        <v>2121</v>
+        <v>2112</v>
       </c>
       <c r="D81" s="6" t="n">
         <v>1508</v>
       </c>
       <c r="E81" s="6" t="n">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="F81" s="6" t="n">
-        <v>854</v>
+        <v>857</v>
       </c>
       <c r="G81" s="6" t="n">
-        <v>751</v>
+        <v>755</v>
       </c>
       <c r="H81" s="6" t="n">
-        <v>708</v>
+        <v>712</v>
       </c>
       <c r="I81" s="6" t="n">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="J81" s="6" t="n">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="K81" s="6" t="n">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="82">
@@ -9740,25 +9740,25 @@
         <v>2976</v>
       </c>
       <c r="C82" s="6" t="n">
-        <v>1606</v>
+        <v>1601</v>
       </c>
       <c r="D82" s="6" t="n">
-        <v>849</v>
+        <v>846</v>
       </c>
       <c r="E82" s="6" t="n">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="F82" s="6" t="n">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="G82" s="6" t="n">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="H82" s="6" t="n">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="I82" s="6" t="n">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="J82" s="6" t="n">
         <v>89</v>
@@ -9777,16 +9777,16 @@
         <v>2688</v>
       </c>
       <c r="C83" s="6" t="n">
-        <v>1294</v>
+        <v>1293</v>
       </c>
       <c r="D83" s="6" t="n">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="E83" s="6" t="n">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F83" s="6" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G83" s="6" t="n">
         <v>54</v>
@@ -9814,25 +9814,25 @@
         <v>2976</v>
       </c>
       <c r="C84" s="6" t="n">
-        <v>1611</v>
+        <v>1613</v>
       </c>
       <c r="D84" s="6" t="n">
-        <v>747</v>
+        <v>750</v>
       </c>
       <c r="E84" s="6" t="n">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="F84" s="6" t="n">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="G84" s="6" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H84" s="6" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I84" s="6" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J84" s="6" t="n">
         <v>1</v>
@@ -9851,19 +9851,19 @@
         <v>2880</v>
       </c>
       <c r="C85" s="6" t="n">
-        <v>1627</v>
+        <v>1623</v>
       </c>
       <c r="D85" s="6" t="n">
-        <v>612</v>
+        <v>615</v>
       </c>
       <c r="E85" s="6" t="n">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="F85" s="6" t="n">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="G85" s="6" t="n">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H85" s="6" t="n">
         <v>133</v>
@@ -9888,10 +9888,10 @@
         <v>2976</v>
       </c>
       <c r="C86" s="6" t="n">
-        <v>644</v>
+        <v>637</v>
       </c>
       <c r="D86" s="6" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E86" s="6" t="n">
         <v>1</v>
@@ -9962,7 +9962,7 @@
         <v>2976</v>
       </c>
       <c r="C88" s="6" t="n">
-        <v>427</v>
+        <v>420</v>
       </c>
       <c r="D88" s="6" t="n">
         <v>37</v>
@@ -9999,7 +9999,7 @@
         <v>2976</v>
       </c>
       <c r="C89" s="6" t="n">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="D89" s="6" t="n">
         <v>97</v>

--- a/outputs/VIC_negative_prices.xlsx
+++ b/outputs/VIC_negative_prices.xlsx
@@ -18,7 +18,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.00&quot;%&quot;"/>
+  </numFmts>
   <fonts count="3">
     <font>
       <name val="Calibri"/>
@@ -74,7 +76,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -6579,108 +6581,12 @@
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B2:B89">
+  <conditionalFormatting sqref="B2:J89">
     <cfRule type="colorScale" priority="1">
       <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="0063BE7B"/>
-        <color rgb="00FFEB84"/>
-        <color rgb="00F8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C89">
-    <cfRule type="colorScale" priority="2">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="0063BE7B"/>
-        <color rgb="00FFEB84"/>
-        <color rgb="00F8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D89">
-    <cfRule type="colorScale" priority="3">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="0063BE7B"/>
-        <color rgb="00FFEB84"/>
-        <color rgb="00F8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E89">
-    <cfRule type="colorScale" priority="4">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="0063BE7B"/>
-        <color rgb="00FFEB84"/>
-        <color rgb="00F8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F89">
-    <cfRule type="colorScale" priority="5">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="0063BE7B"/>
-        <color rgb="00FFEB84"/>
-        <color rgb="00F8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G89">
-    <cfRule type="colorScale" priority="6">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="0063BE7B"/>
-        <color rgb="00FFEB84"/>
-        <color rgb="00F8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H89">
-    <cfRule type="colorScale" priority="7">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="0063BE7B"/>
-        <color rgb="00FFEB84"/>
-        <color rgb="00F8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I89">
-    <cfRule type="colorScale" priority="8">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="0063BE7B"/>
-        <color rgb="00FFEB84"/>
-        <color rgb="00F8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J89">
-    <cfRule type="colorScale" priority="9">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="10"/>
+        <cfvo type="num" val="50"/>
         <color rgb="0063BE7B"/>
         <color rgb="00FFEB84"/>
         <color rgb="00F8696B"/>
